--- a/7. Brasil inputs/data EPE/Calculo da Demanda.xlsx
+++ b/7. Brasil inputs/data EPE/Calculo da Demanda.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SIN-model\7. Brasil inputs\data EPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C371C0-1019-4B5F-BEB4-2F722273EC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7345002E-EC1A-428B-AF3F-C4B2465E3728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F804509D-198A-416F-8845-EE03261C4E2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha3" sheetId="3" r:id="rId1"/>
-    <sheet name="Duracao" sheetId="1" r:id="rId2"/>
-    <sheet name="Pu media" sheetId="4" r:id="rId3"/>
+    <sheet name="MDI vs caderno" sheetId="5" r:id="rId2"/>
+    <sheet name="Duracao" sheetId="1" r:id="rId3"/>
+    <sheet name="Pu media" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
-    <pivotCache cacheId="4" r:id="rId5"/>
-    <pivotCache cacheId="10" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="64">
   <si>
     <t>CARGA(P.U.DEMANDA MED.)</t>
   </si>
@@ -249,6 +250,18 @@
   <si>
     <t>Resultado final</t>
   </si>
+  <si>
+    <t>MDI antes</t>
+  </si>
+  <si>
+    <t>MDI depois</t>
+  </si>
+  <si>
+    <t>histórico</t>
+  </si>
+  <si>
+    <t>Caderno Ref. PDE</t>
+  </si>
 </sst>
 </file>
 
@@ -256,8 +269,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -380,7 +393,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -409,475 +422,114 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{6F28FF4B-9EF3-4029-AF61-93756C203C97}"/>
   </cellStyles>
-  <dxfs count="151">
+  <dxfs count="31">
     <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
+      <numFmt numFmtId="166" formatCode="0.00000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1921,6 +1573,1021 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Comparação Dados Demanda</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MDI vs caderno'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>histórico</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'MDI vs caderno'!$A$2:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2038</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'MDI vs caderno'!$B$2:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>68.180999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67.885999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70.837999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72.313999999999993</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>74.97</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>77.037000000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3FD4-4BEB-B68A-183E5F91997F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MDI vs caderno'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Caderno Ref. PDE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'MDI vs caderno'!$A$2:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2038</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'MDI vs caderno'!$D$2:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="6">
+                  <c:v>77.037000000000006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>79.840999999999994</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>82.350999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>85.302999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>87.959000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>91.058999999999997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>93.863</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>96.814999999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>99.768000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>103.16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>106.26</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3FD4-4BEB-B68A-183E5F91997F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MDI vs caderno'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MDI depois</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'MDI vs caderno'!$A$2:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2029</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2030</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2032</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2033</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2035</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2036</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2037</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2038</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'MDI vs caderno'!$E$2:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="6">
+                  <c:v>78.247219142140082</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>79.109522016883403</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>81.161460073009366</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>83.382355920602322</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>85.907544375998171</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>88.663691763632201</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>91.3843430298882</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>94.246510495094682</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>97.196903148528392</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>100.43135843029889</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>103.67630333105178</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>107.01003536390598</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>110.54297650011409</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>114.20600764316677</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>117.87746794433035</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3FD4-4BEB-B68A-183E5F91997F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="131561408"/>
+        <c:axId val="131571968"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'MDI vs caderno'!$C$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>MDI antes</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'MDI vs caderno'!$A$2:$A$22</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="21"/>
+                      <c:pt idx="0">
+                        <c:v>2018</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2019</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2020</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2021</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2022</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2023</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2024</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>2025</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>2026</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>2027</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>2028</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>2029</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>2030</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>2031</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>2032</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>2033</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>2034</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>2035</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>2036</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>2037</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>2038</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'MDI vs caderno'!$C$2:$C$22</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="21"/>
+                      <c:pt idx="6">
+                        <c:v>95.30720967373945</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>96.357517681952999</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>98.856833219256231</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>101.56194387405887</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>104.63769107916951</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>107.99475245265799</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>111.30857859913301</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>114.79477526808122</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>118.38843258042436</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>122.32808578599133</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>126.28051562856491</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>130.3410905772302</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>134.64430755190511</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>139.10597764088524</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>143.57791467031711</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-3FD4-4BEB-B68A-183E5F91997F}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="131561408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="131571968"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="131571968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="60"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>Demanda (GWm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="131561408"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -3028,6 +3695,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -3545,6 +4252,509 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4102,6 +5312,47 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E280C5C0-797E-2A50-B8BB-2A53216F72F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -8033,7 +9284,7 @@
     <dataField name="Soma de demanda" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="150">
+    <format dxfId="15">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
@@ -8104,7 +9355,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{465653B1-17D1-4D92-AB61-CE1CAD2C913E}" name="Tabela dinâmica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{465653B1-17D1-4D92-AB61-CE1CAD2C913E}" name="Tabela dinâmica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="J28:N44" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" numFmtId="17" showAll="0">
@@ -8429,7 +9680,7 @@
     <dataField name="Média de Bloco 4" fld="4" subtotal="average" baseField="7" baseItem="1"/>
   </dataFields>
   <formats count="15">
-    <format dxfId="119">
+    <format dxfId="30">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8438,7 +9689,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="117">
+    <format dxfId="29">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8447,7 +9698,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="115">
+    <format dxfId="28">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8456,7 +9707,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="113">
+    <format dxfId="27">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8465,7 +9716,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="111">
+    <format dxfId="26">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8474,7 +9725,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="109">
+    <format dxfId="25">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8483,7 +9734,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="107">
+    <format dxfId="24">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8492,7 +9743,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="105">
+    <format dxfId="23">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8501,7 +9752,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="103">
+    <format dxfId="22">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8510,7 +9761,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="101">
+    <format dxfId="21">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8519,7 +9770,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="99">
+    <format dxfId="20">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8528,7 +9779,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="97">
+    <format dxfId="19">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8537,7 +9788,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="95">
+    <format dxfId="18">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8546,7 +9797,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="93">
+    <format dxfId="17">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8555,7 +9806,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="91">
+    <format dxfId="16">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -8616,7 +9867,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{795E0AEA-429A-4AB4-85D6-794ABD9EC3E7}" name="Tabela dinâmica2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{795E0AEA-429A-4AB4-85D6-794ABD9EC3E7}" name="Tabela dinâmica2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H57:L73" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField axis="axisRow" numFmtId="17" showAll="0">
@@ -9306,7 +10557,7 @@
     <dataField name="Média de 4" fld="4" subtotal="average" baseField="7" baseItem="1"/>
   </dataFields>
   <formats count="15">
-    <format dxfId="29">
+    <format dxfId="14">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9315,7 +10566,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="13">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9324,7 +10575,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="12">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9333,7 +10584,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="11">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9342,7 +10593,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="10">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9351,7 +10602,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="9">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9360,7 +10611,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9369,7 +10620,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9378,7 +10629,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="6">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9387,7 +10638,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="5">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9396,7 +10647,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="4">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9405,7 +10656,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9414,7 +10665,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="2">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9423,7 +10674,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -9432,7 +10683,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="0">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="7" count="1">
@@ -10134,6 +11385,335 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25593D73-541E-4C63-B06E-AE20C843D48F}">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1">
+        <v>0.82099999999999995</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2018</v>
+      </c>
+      <c r="B2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2019</v>
+      </c>
+      <c r="B3">
+        <v>68.180999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2020</v>
+      </c>
+      <c r="B4">
+        <v>67.885999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5">
+        <v>70.837999999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2022</v>
+      </c>
+      <c r="B6">
+        <v>72.313999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2023</v>
+      </c>
+      <c r="B7">
+        <v>74.97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8">
+        <v>77.037000000000006</v>
+      </c>
+      <c r="C8">
+        <v>95.30720967373945</v>
+      </c>
+      <c r="D8">
+        <v>77.037000000000006</v>
+      </c>
+      <c r="E8">
+        <f>C8*$F$1</f>
+        <v>78.247219142140082</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2025</v>
+      </c>
+      <c r="C9">
+        <v>96.357517681952999</v>
+      </c>
+      <c r="D9">
+        <v>79.840999999999994</v>
+      </c>
+      <c r="E9">
+        <f>C9*$F$1</f>
+        <v>79.109522016883403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2026</v>
+      </c>
+      <c r="C10">
+        <v>98.856833219256231</v>
+      </c>
+      <c r="D10">
+        <v>82.350999999999999</v>
+      </c>
+      <c r="E10">
+        <f>C10*$F$1</f>
+        <v>81.161460073009366</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2027</v>
+      </c>
+      <c r="C11">
+        <v>101.56194387405887</v>
+      </c>
+      <c r="D11">
+        <v>85.302999999999997</v>
+      </c>
+      <c r="E11">
+        <f>C11*$F$1</f>
+        <v>83.382355920602322</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2028</v>
+      </c>
+      <c r="C12">
+        <v>104.63769107916951</v>
+      </c>
+      <c r="D12">
+        <v>87.959000000000003</v>
+      </c>
+      <c r="E12">
+        <f>C12*$F$1</f>
+        <v>85.907544375998171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2029</v>
+      </c>
+      <c r="C13">
+        <v>107.99475245265799</v>
+      </c>
+      <c r="D13">
+        <v>91.058999999999997</v>
+      </c>
+      <c r="E13">
+        <f>C13*$F$1</f>
+        <v>88.663691763632201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2030</v>
+      </c>
+      <c r="C14">
+        <v>111.30857859913301</v>
+      </c>
+      <c r="D14">
+        <v>93.863</v>
+      </c>
+      <c r="E14">
+        <f>C14*$F$1</f>
+        <v>91.3843430298882</v>
+      </c>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2031</v>
+      </c>
+      <c r="C15">
+        <v>114.79477526808122</v>
+      </c>
+      <c r="D15">
+        <v>96.814999999999998</v>
+      </c>
+      <c r="E15">
+        <f>C15*$F$1</f>
+        <v>94.246510495094682</v>
+      </c>
+      <c r="J15" s="19"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2032</v>
+      </c>
+      <c r="C16">
+        <v>118.38843258042436</v>
+      </c>
+      <c r="D16">
+        <v>99.768000000000001</v>
+      </c>
+      <c r="E16">
+        <f>C16*$F$1</f>
+        <v>97.196903148528392</v>
+      </c>
+      <c r="J16" s="19"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2033</v>
+      </c>
+      <c r="C17">
+        <v>122.32808578599133</v>
+      </c>
+      <c r="D17">
+        <v>103.16</v>
+      </c>
+      <c r="E17">
+        <f>C17*$F$1</f>
+        <v>100.43135843029889</v>
+      </c>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2034</v>
+      </c>
+      <c r="C18">
+        <v>126.28051562856491</v>
+      </c>
+      <c r="D18">
+        <v>106.26</v>
+      </c>
+      <c r="E18">
+        <f>C18*$F$1</f>
+        <v>103.67630333105178</v>
+      </c>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2035</v>
+      </c>
+      <c r="C19">
+        <v>130.3410905772302</v>
+      </c>
+      <c r="E19">
+        <f>C19*$F$1</f>
+        <v>107.01003536390598</v>
+      </c>
+      <c r="J19" s="19"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2036</v>
+      </c>
+      <c r="C20">
+        <v>134.64430755190511</v>
+      </c>
+      <c r="E20">
+        <f>C20*$F$1</f>
+        <v>110.54297650011409</v>
+      </c>
+      <c r="J20" s="19"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2037</v>
+      </c>
+      <c r="C21">
+        <v>139.10597764088524</v>
+      </c>
+      <c r="E21">
+        <f>C21*$F$1</f>
+        <v>114.20600764316677</v>
+      </c>
+      <c r="J21" s="19"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2038</v>
+      </c>
+      <c r="C22">
+        <v>143.57791467031711</v>
+      </c>
+      <c r="E22">
+        <f>C22*$F$1</f>
+        <v>117.87746794433035</v>
+      </c>
+      <c r="J22" s="19"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J23" s="19"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J25" s="19"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J26" s="19"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J27" s="19"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J28" s="19"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J29" s="19"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J30" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D736287E-5306-43AF-9B42-BA3C78F3D6D1}">
   <dimension ref="C1:Z207"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10144,22 +11724,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:26" x14ac:dyDescent="0.3">
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
       <c r="Y1" t="s">
         <v>26</v>
       </c>
@@ -10839,11 +12419,11 @@
         <f>AVERAGE(F15:Q15)</f>
         <v>644.09729758166668</v>
       </c>
-      <c r="S15" s="17">
+      <c r="S15" s="15">
         <f>R15/$R$4</f>
         <v>1.8841609999999998E-2</v>
       </c>
-      <c r="T15" s="17">
+      <c r="T15" s="15">
         <f>E15*E8</f>
         <v>1.8841610000000002E-2</v>
       </c>
@@ -10923,11 +12503,11 @@
         <f t="shared" ref="R16:R18" si="7">AVERAGE(F16:Q16)</f>
         <v>14251.593774724999</v>
       </c>
-      <c r="S16" s="17">
+      <c r="S16" s="15">
         <f t="shared" ref="S16:S18" si="8">R16/$R$4</f>
         <v>0.41689814999999997</v>
       </c>
-      <c r="T16" s="17">
+      <c r="T16" s="15">
         <f t="shared" ref="T16:T18" si="9">E16*E9</f>
         <v>0.41689815000000002</v>
       </c>
@@ -11007,11 +12587,11 @@
         <f t="shared" si="7"/>
         <v>15492.576038419997</v>
       </c>
-      <c r="S17" s="17">
+      <c r="S17" s="15">
         <f t="shared" si="8"/>
         <v>0.45320027999999984</v>
       </c>
-      <c r="T17" s="17">
+      <c r="T17" s="15">
         <f t="shared" si="9"/>
         <v>0.45320028000000001</v>
       </c>
@@ -11091,11 +12671,11 @@
         <f t="shared" si="7"/>
         <v>3796.8465382399995</v>
       </c>
-      <c r="S18" s="17">
+      <c r="S18" s="15">
         <f t="shared" si="8"/>
         <v>0.11106815999999997</v>
       </c>
-      <c r="T18" s="17">
+      <c r="T18" s="15">
         <f t="shared" si="9"/>
         <v>0.11106815999999999</v>
       </c>
@@ -11135,51 +12715,51 @@
       </c>
     </row>
     <row r="20" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="F20" s="15">
+      <c r="F20" s="8">
         <f>F14-F7</f>
         <v>0.31392879999475554</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="8">
         <f t="shared" ref="G20:Q20" si="12">G14-G7</f>
         <v>0.31187059999501798</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="8">
         <f t="shared" si="12"/>
         <v>0.30988619998970535</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="8">
         <f t="shared" si="12"/>
         <v>0.27738959999987856</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="8">
         <f t="shared" si="12"/>
         <v>0.25939060000018799</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="8">
         <f t="shared" si="12"/>
         <v>0.25432300000102259</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="8">
         <f t="shared" si="12"/>
         <v>0.25220740000077058</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="8">
         <f t="shared" si="12"/>
         <v>0.25829179999709595</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20" s="8">
         <f t="shared" si="12"/>
         <v>0.2755200000028708</v>
       </c>
-      <c r="O20" s="15">
+      <c r="O20" s="8">
         <f t="shared" si="12"/>
         <v>0.2813666000001831</v>
       </c>
-      <c r="P20" s="15">
+      <c r="P20" s="8">
         <f t="shared" si="12"/>
         <v>0.27972659999795724</v>
       </c>
-      <c r="Q20" s="15">
+      <c r="Q20" s="8">
         <f t="shared" si="12"/>
         <v>0.28988640000170562</v>
       </c>
@@ -11267,7 +12847,7 @@
         <f t="shared" si="13"/>
         <v>666.08859671999994</v>
       </c>
-      <c r="S22" s="17"/>
+      <c r="S22" s="15"/>
       <c r="U22">
         <v>17</v>
       </c>
@@ -11334,7 +12914,7 @@
         <f t="shared" si="14"/>
         <v>14738.1833988</v>
       </c>
-      <c r="S23" s="17"/>
+      <c r="S23" s="15"/>
       <c r="U23">
         <v>18</v>
       </c>
@@ -11401,7 +12981,7 @@
         <f t="shared" si="15"/>
         <v>16021.53629856</v>
       </c>
-      <c r="S24" s="17"/>
+      <c r="S24" s="15"/>
       <c r="U24">
         <v>19</v>
       </c>
@@ -11468,7 +13048,7 @@
         <f t="shared" si="16"/>
         <v>3926.4815923199994</v>
       </c>
-      <c r="S25" s="17"/>
+      <c r="S25" s="15"/>
       <c r="U25">
         <v>20</v>
       </c>
@@ -11621,16 +13201,16 @@
       <c r="J29" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="14">
         <v>0.33056666666666668</v>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="14">
         <v>0.48035</v>
       </c>
-      <c r="N29" s="16">
+      <c r="N29" s="14">
         <v>0.17538333333333334</v>
       </c>
       <c r="O29" s="8"/>
@@ -11674,16 +13254,16 @@
       <c r="J30" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="14">
         <v>0.33115</v>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="14">
         <v>0.48067500000000002</v>
       </c>
-      <c r="N30" s="16">
+      <c r="N30" s="14">
         <v>0.17447500000000002</v>
       </c>
       <c r="O30" s="8"/>
@@ -11727,16 +13307,16 @@
       <c r="J31" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="14">
         <v>0.33188333333333336</v>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="14">
         <v>0.4751083333333333</v>
       </c>
-      <c r="N31" s="16">
+      <c r="N31" s="14">
         <v>0.17930833333333332</v>
       </c>
       <c r="O31" s="8"/>
@@ -11780,16 +13360,16 @@
       <c r="J32" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="14">
         <v>0.33288333333333336</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="14">
         <v>0.47444166666666659</v>
       </c>
-      <c r="N32" s="16">
+      <c r="N32" s="14">
         <v>0.17897500000000002</v>
       </c>
       <c r="O32" s="8"/>
@@ -11831,16 +13411,16 @@
       <c r="J33" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="14">
         <v>0.33431666666666665</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="14">
         <v>0.47569166666666668</v>
       </c>
-      <c r="N33" s="16">
+      <c r="N33" s="14">
         <v>0.17629166666666665</v>
       </c>
       <c r="U33">
@@ -11879,16 +13459,16 @@
       <c r="J34" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="14">
         <v>0.33539166666666659</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="14">
         <v>0.47460833333333335</v>
       </c>
-      <c r="N34" s="16">
+      <c r="N34" s="14">
         <v>0.17629999999999998</v>
       </c>
       <c r="U34">
@@ -11927,16 +13507,16 @@
       <c r="J35" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="14">
         <v>0.33644166666666669</v>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="14">
         <v>0.47457499999999997</v>
       </c>
-      <c r="N35" s="16">
+      <c r="N35" s="14">
         <v>0.17528333333333335</v>
       </c>
       <c r="U35">
@@ -11975,16 +13555,16 @@
       <c r="J36" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="14">
         <v>0.33750833333333335</v>
       </c>
-      <c r="M36" s="16">
+      <c r="M36" s="14">
         <v>0.47548333333333331</v>
       </c>
-      <c r="N36" s="16">
+      <c r="N36" s="14">
         <v>0.17330833333333331</v>
       </c>
       <c r="U36">
@@ -12023,16 +13603,16 @@
       <c r="J37" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L37" s="16">
+      <c r="L37" s="14">
         <v>0.33922500000000005</v>
       </c>
-      <c r="M37" s="16">
+      <c r="M37" s="14">
         <v>0.47866666666666674</v>
       </c>
-      <c r="N37" s="16">
+      <c r="N37" s="14">
         <v>0.16840833333333335</v>
       </c>
       <c r="U37">
@@ -12071,16 +13651,16 @@
       <c r="J38" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="14">
         <v>0.33966666666666673</v>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="14">
         <v>0.47950833333333326</v>
       </c>
-      <c r="N38" s="16">
+      <c r="N38" s="14">
         <v>0.167125</v>
       </c>
       <c r="U38">
@@ -12119,16 +13699,16 @@
       <c r="J39" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K39" s="16">
+      <c r="K39" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L39" s="16">
+      <c r="L39" s="14">
         <v>0.34071666666666672</v>
       </c>
-      <c r="M39" s="16">
+      <c r="M39" s="14">
         <v>0.48171666666666663</v>
       </c>
-      <c r="N39" s="16">
+      <c r="N39" s="14">
         <v>0.16386666666666663</v>
       </c>
       <c r="U39">
@@ -12167,16 +13747,16 @@
       <c r="J40" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L40" s="16">
+      <c r="L40" s="14">
         <v>0.34160000000000007</v>
       </c>
-      <c r="M40" s="16">
+      <c r="M40" s="14">
         <v>0.48371666666666657</v>
       </c>
-      <c r="N40" s="16">
+      <c r="N40" s="14">
         <v>0.16098333333333334</v>
       </c>
       <c r="U40">
@@ -12215,16 +13795,16 @@
       <c r="J41" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="K41" s="16">
+      <c r="K41" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L41" s="16">
+      <c r="L41" s="14">
         <v>0.33190000000000003</v>
       </c>
-      <c r="M41" s="16">
+      <c r="M41" s="14">
         <v>0.48249999999999993</v>
       </c>
-      <c r="N41" s="16">
+      <c r="N41" s="14">
         <v>0.17190000000000003</v>
       </c>
       <c r="U41">
@@ -12263,16 +13843,16 @@
       <c r="J42" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L42" s="16">
+      <c r="L42" s="14">
         <v>0.34339999999999998</v>
       </c>
-      <c r="M42" s="16">
+      <c r="M42" s="14">
         <v>0.48777500000000001</v>
       </c>
-      <c r="N42" s="16">
+      <c r="N42" s="14">
         <v>0.15512499999999999</v>
       </c>
       <c r="U42">
@@ -12311,16 +13891,16 @@
       <c r="J43" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="14">
         <v>1.3699999999999999E-2</v>
       </c>
-      <c r="L43" s="16">
+      <c r="L43" s="14">
         <v>0.34425</v>
       </c>
-      <c r="M43" s="16">
+      <c r="M43" s="14">
         <v>0.48926666666666668</v>
       </c>
-      <c r="N43" s="16">
+      <c r="N43" s="14">
         <v>0.1527833333333333</v>
       </c>
       <c r="U43">
@@ -12359,16 +13939,16 @@
       <c r="J44" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="18">
+      <c r="K44">
         <v>1.3700000000000033E-2</v>
       </c>
-      <c r="L44" s="18">
+      <c r="L44">
         <v>0.33672666666666667</v>
       </c>
-      <c r="M44" s="18">
+      <c r="M44">
         <v>0.47960555555555562</v>
       </c>
-      <c r="N44" s="18">
+      <c r="N44">
         <v>0.16996777777777766</v>
       </c>
       <c r="U44">
@@ -12522,7 +14102,7 @@
       <c r="G48" s="3">
         <v>0.18640000000000001</v>
       </c>
-      <c r="J48" s="20">
+      <c r="J48" s="17">
         <v>1.3700000000000033E-2</v>
       </c>
       <c r="K48" cm="1">
@@ -12562,7 +14142,7 @@
       <c r="G49" s="3">
         <v>0.1961</v>
       </c>
-      <c r="J49" s="20">
+      <c r="J49" s="17">
         <v>0.33672666666666667</v>
       </c>
       <c r="K49">
@@ -12601,7 +14181,7 @@
       <c r="G50" s="3">
         <v>0.18429999999999999</v>
       </c>
-      <c r="J50" s="20">
+      <c r="J50" s="17">
         <v>0.47960555555555562</v>
       </c>
       <c r="K50">
@@ -12640,7 +14220,7 @@
       <c r="G51" s="3">
         <v>0.21160000000000001</v>
       </c>
-      <c r="J51" s="20">
+      <c r="J51" s="17">
         <v>0.16996777777777766</v>
       </c>
       <c r="K51">
@@ -15534,7 +17114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE06370-E4E0-46D5-90C7-57A01AE00591}">
   <dimension ref="A1:FY236"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -35367,723 +36947,723 @@
       <c r="A45" s="2">
         <v>1</v>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="16">
         <f>AVERAGE(B39,B33,B27,B21,B15,B9,B3)</f>
         <v>1.2999142857142856</v>
       </c>
-      <c r="C45" s="19">
+      <c r="C45" s="16">
         <f t="shared" ref="C45:BN45" si="0">AVERAGE(C39,C33,C27,C21,C15,C9,C3)</f>
         <v>1.3134857142857144</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="16">
         <f t="shared" si="0"/>
         <v>1.3382000000000001</v>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="16">
         <f t="shared" si="0"/>
         <v>1.3547428571428572</v>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="16">
         <f t="shared" si="0"/>
         <v>1.4460571428571427</v>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="16">
         <f t="shared" si="0"/>
         <v>1.3947714285714283</v>
       </c>
-      <c r="H45" s="19">
+      <c r="H45" s="16">
         <f t="shared" si="0"/>
         <v>1.3970714285714287</v>
       </c>
-      <c r="I45" s="19">
+      <c r="I45" s="16">
         <f t="shared" si="0"/>
         <v>1.3382857142857143</v>
       </c>
-      <c r="J45" s="19">
+      <c r="J45" s="16">
         <f t="shared" si="0"/>
         <v>1.2671142857142859</v>
       </c>
-      <c r="K45" s="19">
+      <c r="K45" s="16">
         <f t="shared" si="0"/>
         <v>1.3326714285714287</v>
       </c>
-      <c r="L45" s="19">
+      <c r="L45" s="16">
         <f t="shared" si="0"/>
         <v>1.3918142857142857</v>
       </c>
-      <c r="M45" s="19">
+      <c r="M45" s="16">
         <f t="shared" si="0"/>
         <v>1.3467857142857143</v>
       </c>
-      <c r="N45" s="19">
+      <c r="N45" s="16">
         <f t="shared" si="0"/>
         <v>1.316057142857143</v>
       </c>
-      <c r="O45" s="19">
+      <c r="O45" s="16">
         <f t="shared" si="0"/>
         <v>1.3247</v>
       </c>
-      <c r="P45" s="19">
+      <c r="P45" s="16">
         <f t="shared" si="0"/>
         <v>1.3659999999999999</v>
       </c>
-      <c r="Q45" s="19">
+      <c r="Q45" s="16">
         <f t="shared" si="0"/>
         <v>1.3711714285714287</v>
       </c>
-      <c r="R45" s="19">
+      <c r="R45" s="16">
         <f t="shared" si="0"/>
         <v>1.4614142857142856</v>
       </c>
-      <c r="S45" s="19">
+      <c r="S45" s="16">
         <f t="shared" si="0"/>
         <v>1.4074428571428572</v>
       </c>
-      <c r="T45" s="19">
+      <c r="T45" s="16">
         <f t="shared" si="0"/>
         <v>1.4097999999999999</v>
       </c>
-      <c r="U45" s="19">
+      <c r="U45" s="16">
         <f t="shared" si="0"/>
         <v>1.3485142857142858</v>
       </c>
-      <c r="V45" s="19">
+      <c r="V45" s="16">
         <f t="shared" si="0"/>
         <v>1.2737428571428571</v>
       </c>
-      <c r="W45" s="19">
+      <c r="W45" s="16">
         <f t="shared" si="0"/>
         <v>1.3422714285714286</v>
       </c>
-      <c r="X45" s="19">
+      <c r="X45" s="16">
         <f t="shared" si="0"/>
         <v>1.4019428571428574</v>
       </c>
-      <c r="Y45" s="19">
+      <c r="Y45" s="16">
         <f t="shared" si="0"/>
         <v>1.3546857142857143</v>
       </c>
-      <c r="Z45" s="19">
+      <c r="Z45" s="16">
         <f t="shared" si="0"/>
         <v>1.3243714285714285</v>
       </c>
-      <c r="AA45" s="19">
+      <c r="AA45" s="16">
         <f t="shared" si="0"/>
         <v>1.3328285714285715</v>
       </c>
-      <c r="AB45" s="19">
+      <c r="AB45" s="16">
         <f t="shared" si="0"/>
         <v>1.3745571428571428</v>
       </c>
-      <c r="AC45" s="19">
+      <c r="AC45" s="16">
         <f t="shared" si="0"/>
         <v>1.3791285714285715</v>
       </c>
-      <c r="AD45" s="19">
+      <c r="AD45" s="16">
         <f t="shared" si="0"/>
         <v>1.4671428571428571</v>
       </c>
-      <c r="AE45" s="19">
+      <c r="AE45" s="16">
         <f t="shared" si="0"/>
         <v>1.4132714285714285</v>
       </c>
-      <c r="AF45" s="19">
+      <c r="AF45" s="16">
         <f t="shared" si="0"/>
         <v>1.4166000000000001</v>
       </c>
-      <c r="AG45" s="19">
+      <c r="AG45" s="16">
         <f t="shared" si="0"/>
         <v>1.3543714285714283</v>
       </c>
-      <c r="AH45" s="19">
+      <c r="AH45" s="16">
         <f t="shared" si="0"/>
         <v>1.2785571428571427</v>
       </c>
-      <c r="AI45" s="19">
+      <c r="AI45" s="16">
         <f t="shared" si="0"/>
         <v>1.3480142857142856</v>
       </c>
-      <c r="AJ45" s="19">
+      <c r="AJ45" s="16">
         <f t="shared" si="0"/>
         <v>1.407057142857143</v>
       </c>
-      <c r="AK45" s="19">
+      <c r="AK45" s="16">
         <f t="shared" si="0"/>
         <v>1.3598999999999999</v>
       </c>
-      <c r="AL45" s="19">
+      <c r="AL45" s="16">
         <f t="shared" si="0"/>
         <v>1.3285</v>
       </c>
-      <c r="AM45" s="19">
+      <c r="AM45" s="16">
         <f t="shared" si="0"/>
         <v>1.3354142857142857</v>
       </c>
-      <c r="AN45" s="19">
+      <c r="AN45" s="16">
         <f t="shared" si="0"/>
         <v>1.377114285714286</v>
       </c>
-      <c r="AO45" s="19">
+      <c r="AO45" s="16">
         <f t="shared" si="0"/>
         <v>1.3820714285714284</v>
       </c>
-      <c r="AP45" s="19">
+      <c r="AP45" s="16">
         <f t="shared" si="0"/>
         <v>1.4700571428571425</v>
       </c>
-      <c r="AQ45" s="19">
+      <c r="AQ45" s="16">
         <f t="shared" si="0"/>
         <v>1.4178714285714287</v>
       </c>
-      <c r="AR45" s="19">
+      <c r="AR45" s="16">
         <f t="shared" si="0"/>
         <v>1.4221857142857142</v>
       </c>
-      <c r="AS45" s="19">
+      <c r="AS45" s="16">
         <f t="shared" si="0"/>
         <v>1.3604857142857143</v>
       </c>
-      <c r="AT45" s="19">
+      <c r="AT45" s="16">
         <f t="shared" si="0"/>
         <v>1.2844142857142857</v>
       </c>
-      <c r="AU45" s="19">
+      <c r="AU45" s="16">
         <f t="shared" si="0"/>
         <v>1.3527285714285711</v>
       </c>
-      <c r="AV45" s="19">
+      <c r="AV45" s="16">
         <f t="shared" si="0"/>
         <v>1.4099571428571427</v>
       </c>
-      <c r="AW45" s="19">
+      <c r="AW45" s="16">
         <f t="shared" si="0"/>
         <v>1.3627714285714287</v>
       </c>
-      <c r="AX45" s="19">
+      <c r="AX45" s="16">
         <f t="shared" si="0"/>
         <v>1.3333285714285714</v>
       </c>
-      <c r="AY45" s="19">
+      <c r="AY45" s="16">
         <f t="shared" si="0"/>
         <v>1.3418142857142856</v>
       </c>
-      <c r="AZ45" s="19">
+      <c r="AZ45" s="16">
         <f t="shared" si="0"/>
         <v>1.3697428571428572</v>
       </c>
-      <c r="BA45" s="19">
+      <c r="BA45" s="16">
         <f t="shared" si="0"/>
         <v>1.3828142857142858</v>
       </c>
-      <c r="BB45" s="19">
+      <c r="BB45" s="16">
         <f t="shared" si="0"/>
         <v>1.4706571428571429</v>
       </c>
-      <c r="BC45" s="19">
+      <c r="BC45" s="16">
         <f t="shared" si="0"/>
         <v>1.4209285714285713</v>
       </c>
-      <c r="BD45" s="19">
+      <c r="BD45" s="16">
         <f t="shared" si="0"/>
         <v>1.4264999999999997</v>
       </c>
-      <c r="BE45" s="19">
+      <c r="BE45" s="16">
         <f t="shared" si="0"/>
         <v>1.365142857142857</v>
       </c>
-      <c r="BF45" s="19">
+      <c r="BF45" s="16">
         <f t="shared" si="0"/>
         <v>1.2891857142857144</v>
       </c>
-      <c r="BG45" s="19">
+      <c r="BG45" s="16">
         <f t="shared" si="0"/>
         <v>1.3556000000000001</v>
       </c>
-      <c r="BH45" s="19">
+      <c r="BH45" s="16">
         <f t="shared" si="0"/>
         <v>1.4106428571428573</v>
       </c>
-      <c r="BI45" s="19">
+      <c r="BI45" s="16">
         <f t="shared" si="0"/>
         <v>1.3641428571428571</v>
       </c>
-      <c r="BJ45" s="19">
+      <c r="BJ45" s="16">
         <f t="shared" si="0"/>
         <v>1.3335285714285714</v>
       </c>
-      <c r="BK45" s="19">
+      <c r="BK45" s="16">
         <f t="shared" si="0"/>
         <v>1.3356571428571427</v>
       </c>
-      <c r="BL45" s="19">
+      <c r="BL45" s="16">
         <f t="shared" si="0"/>
         <v>1.3767285714285715</v>
       </c>
-      <c r="BM45" s="19">
+      <c r="BM45" s="16">
         <f t="shared" si="0"/>
         <v>1.3825428571428573</v>
       </c>
-      <c r="BN45" s="19">
+      <c r="BN45" s="16">
         <f t="shared" si="0"/>
         <v>1.4707142857142856</v>
       </c>
-      <c r="BO45" s="19">
+      <c r="BO45" s="16">
         <f t="shared" ref="BO45:DZ45" si="1">AVERAGE(BO39,BO33,BO27,BO21,BO15,BO9,BO3)</f>
         <v>1.4265142857142858</v>
       </c>
-      <c r="BP45" s="19">
+      <c r="BP45" s="16">
         <f t="shared" si="1"/>
         <v>1.4344999999999999</v>
       </c>
-      <c r="BQ45" s="19">
+      <c r="BQ45" s="16">
         <f t="shared" si="1"/>
         <v>1.3747</v>
       </c>
-      <c r="BR45" s="19">
+      <c r="BR45" s="16">
         <f t="shared" si="1"/>
         <v>1.296442857142857</v>
       </c>
-      <c r="BS45" s="19">
+      <c r="BS45" s="16">
         <f t="shared" si="1"/>
         <v>1.3614571428571429</v>
       </c>
-      <c r="BT45" s="19">
+      <c r="BT45" s="16">
         <f t="shared" si="1"/>
         <v>1.4131571428571428</v>
       </c>
-      <c r="BU45" s="19">
+      <c r="BU45" s="16">
         <f t="shared" si="1"/>
         <v>1.3660999999999999</v>
       </c>
-      <c r="BV45" s="19">
+      <c r="BV45" s="16">
         <f t="shared" si="1"/>
         <v>1.3338285714285714</v>
       </c>
-      <c r="BW45" s="19">
+      <c r="BW45" s="16">
         <f t="shared" si="1"/>
         <v>1.3350000000000002</v>
       </c>
-      <c r="BX45" s="19">
+      <c r="BX45" s="16">
         <f t="shared" si="1"/>
         <v>1.3757714285714289</v>
       </c>
-      <c r="BY45" s="19">
+      <c r="BY45" s="16">
         <f t="shared" si="1"/>
         <v>1.3818142857142859</v>
       </c>
-      <c r="BZ45" s="19">
+      <c r="BZ45" s="16">
         <f t="shared" si="1"/>
         <v>1.4698999999999998</v>
       </c>
-      <c r="CA45" s="19">
+      <c r="CA45" s="16">
         <f t="shared" si="1"/>
         <v>1.4288999999999998</v>
       </c>
-      <c r="CB45" s="19">
+      <c r="CB45" s="16">
         <f t="shared" si="1"/>
         <v>1.4388714285714286</v>
       </c>
-      <c r="CC45" s="19">
+      <c r="CC45" s="16">
         <f t="shared" si="1"/>
         <v>1.3798428571428569</v>
       </c>
-      <c r="CD45" s="19">
+      <c r="CD45" s="16">
         <f t="shared" si="1"/>
         <v>1.3008857142857144</v>
       </c>
-      <c r="CE45" s="19">
+      <c r="CE45" s="16">
         <f t="shared" si="1"/>
         <v>1.3638571428571427</v>
       </c>
-      <c r="CF45" s="19">
+      <c r="CF45" s="16">
         <f t="shared" si="1"/>
         <v>1.4133142857142857</v>
       </c>
-      <c r="CG45" s="19">
+      <c r="CG45" s="16">
         <f t="shared" si="1"/>
         <v>1.3662571428571426</v>
       </c>
-      <c r="CH45" s="19">
+      <c r="CH45" s="16">
         <f t="shared" si="1"/>
         <v>1.3340142857142856</v>
       </c>
-      <c r="CI45" s="19">
+      <c r="CI45" s="16">
         <f t="shared" si="1"/>
         <v>1.3339571428571426</v>
       </c>
-      <c r="CJ45" s="19">
+      <c r="CJ45" s="16">
         <f t="shared" si="1"/>
         <v>1.3742428571428571</v>
       </c>
-      <c r="CK45" s="19">
+      <c r="CK45" s="16">
         <f t="shared" si="1"/>
         <v>1.3804000000000001</v>
       </c>
-      <c r="CL45" s="19">
+      <c r="CL45" s="16">
         <f t="shared" si="1"/>
         <v>1.4680428571428572</v>
       </c>
-      <c r="CM45" s="19">
+      <c r="CM45" s="16">
         <f t="shared" si="1"/>
         <v>1.4308571428571428</v>
       </c>
-      <c r="CN45" s="19">
+      <c r="CN45" s="16">
         <f t="shared" si="1"/>
         <v>1.4429571428571428</v>
       </c>
-      <c r="CO45" s="19">
+      <c r="CO45" s="16">
         <f t="shared" si="1"/>
         <v>1.3848285714285713</v>
       </c>
-      <c r="CP45" s="19">
+      <c r="CP45" s="16">
         <f t="shared" si="1"/>
         <v>1.3049428571428572</v>
       </c>
-      <c r="CQ45" s="19">
+      <c r="CQ45" s="16">
         <f t="shared" si="1"/>
         <v>1.3653571428571429</v>
       </c>
-      <c r="CR45" s="19">
+      <c r="CR45" s="16">
         <f t="shared" si="1"/>
         <v>1.4134285714285717</v>
       </c>
-      <c r="CS45" s="19">
+      <c r="CS45" s="16">
         <f t="shared" si="1"/>
         <v>1.3647428571428573</v>
       </c>
-      <c r="CT45" s="19">
+      <c r="CT45" s="16">
         <f t="shared" si="1"/>
         <v>1.3333285714285714</v>
       </c>
-      <c r="CU45" s="19">
+      <c r="CU45" s="16">
         <f t="shared" si="1"/>
         <v>1.3365571428571428</v>
       </c>
-      <c r="CV45" s="19">
+      <c r="CV45" s="16">
         <f t="shared" si="1"/>
         <v>1.3639428571428573</v>
       </c>
-      <c r="CW45" s="19">
+      <c r="CW45" s="16">
         <f t="shared" si="1"/>
         <v>1.3780428571428571</v>
       </c>
-      <c r="CX45" s="19">
+      <c r="CX45" s="16">
         <f t="shared" si="1"/>
         <v>1.4652142857142856</v>
       </c>
-      <c r="CY45" s="19">
+      <c r="CY45" s="16">
         <f t="shared" si="1"/>
         <v>1.431657142857143</v>
       </c>
-      <c r="CZ45" s="19">
+      <c r="CZ45" s="16">
         <f t="shared" si="1"/>
         <v>1.4461142857142857</v>
       </c>
-      <c r="DA45" s="19">
+      <c r="DA45" s="16">
         <f t="shared" si="1"/>
         <v>1.3890714285714285</v>
       </c>
-      <c r="DB45" s="19">
+      <c r="DB45" s="16">
         <f t="shared" si="1"/>
         <v>1.3085714285714285</v>
       </c>
-      <c r="DC45" s="19">
+      <c r="DC45" s="16">
         <f t="shared" si="1"/>
         <v>1.3658714285714286</v>
       </c>
-      <c r="DD45" s="19">
+      <c r="DD45" s="16">
         <f t="shared" si="1"/>
         <v>1.4110571428571428</v>
       </c>
-      <c r="DE45" s="19">
+      <c r="DE45" s="16">
         <f t="shared" si="1"/>
         <v>1.3628285714285713</v>
       </c>
-      <c r="DF45" s="19">
+      <c r="DF45" s="16">
         <f t="shared" si="1"/>
         <v>1.3305142857142855</v>
       </c>
-      <c r="DG45" s="19">
+      <c r="DG45" s="16">
         <f t="shared" si="1"/>
         <v>1.3282857142857143</v>
       </c>
-      <c r="DH45" s="19">
+      <c r="DH45" s="16">
         <f t="shared" si="1"/>
         <v>1.3679714285714286</v>
       </c>
-      <c r="DI45" s="19">
+      <c r="DI45" s="16">
         <f t="shared" si="1"/>
         <v>1.3742999999999999</v>
       </c>
-      <c r="DJ45" s="19">
+      <c r="DJ45" s="16">
         <f t="shared" si="1"/>
         <v>1.4610428571428571</v>
       </c>
-      <c r="DK45" s="19">
+      <c r="DK45" s="16">
         <f t="shared" si="1"/>
         <v>1.4314000000000002</v>
       </c>
-      <c r="DL45" s="19">
+      <c r="DL45" s="16">
         <f t="shared" si="1"/>
         <v>1.4487142857142856</v>
       </c>
-      <c r="DM45" s="19">
+      <c r="DM45" s="16">
         <f t="shared" si="1"/>
         <v>1.3932</v>
       </c>
-      <c r="DN45" s="19">
+      <c r="DN45" s="16">
         <f t="shared" si="1"/>
         <v>1.3115142857142856</v>
       </c>
-      <c r="DO45" s="19">
+      <c r="DO45" s="16">
         <f t="shared" si="1"/>
         <v>1.3661285714285714</v>
       </c>
-      <c r="DP45" s="19">
+      <c r="DP45" s="16">
         <f t="shared" si="1"/>
         <v>1.4093571428571428</v>
       </c>
-      <c r="DQ45" s="19">
+      <c r="DQ45" s="16">
         <f t="shared" si="1"/>
         <v>1.3602142857142856</v>
       </c>
-      <c r="DR45" s="19">
+      <c r="DR45" s="16">
         <f t="shared" si="1"/>
         <v>1.3284142857142858</v>
       </c>
-      <c r="DS45" s="19">
+      <c r="DS45" s="16">
         <f t="shared" si="1"/>
         <v>1.3251285714285714</v>
       </c>
-      <c r="DT45" s="19">
+      <c r="DT45" s="16">
         <f t="shared" si="1"/>
         <v>1.3644999999999998</v>
       </c>
-      <c r="DU45" s="19">
+      <c r="DU45" s="16">
         <f t="shared" si="1"/>
         <v>1.3709285714285715</v>
       </c>
-      <c r="DV45" s="19">
+      <c r="DV45" s="16">
         <f t="shared" si="1"/>
         <v>1.4570714285714286</v>
       </c>
-      <c r="DW45" s="19">
+      <c r="DW45" s="16">
         <f t="shared" si="1"/>
         <v>1.4311</v>
       </c>
-      <c r="DX45" s="19">
+      <c r="DX45" s="16">
         <f t="shared" si="1"/>
         <v>1.451057142857143</v>
       </c>
-      <c r="DY45" s="19">
+      <c r="DY45" s="16">
         <f t="shared" si="1"/>
         <v>1.397342857142857</v>
       </c>
-      <c r="DZ45" s="19">
+      <c r="DZ45" s="16">
         <f t="shared" si="1"/>
         <v>1.3146428571428572</v>
       </c>
-      <c r="EA45" s="19">
+      <c r="EA45" s="16">
         <f t="shared" ref="EA45:FY45" si="2">AVERAGE(EA39,EA33,EA27,EA21,EA15,EA9,EA3)</f>
         <v>1.3658999999999999</v>
       </c>
-      <c r="EB45" s="19">
+      <c r="EB45" s="16">
         <f t="shared" si="2"/>
         <v>1.4068428571428571</v>
       </c>
-      <c r="EC45" s="19">
+      <c r="EC45" s="16">
         <f t="shared" si="2"/>
         <v>1.3575999999999999</v>
       </c>
-      <c r="ED45" s="19">
+      <c r="ED45" s="16">
         <f t="shared" si="2"/>
         <v>1.3261714285714288</v>
       </c>
-      <c r="EE45" s="19">
+      <c r="EE45" s="16">
         <f t="shared" si="2"/>
         <v>1.3219285714285713</v>
       </c>
-      <c r="EF45" s="19">
+      <c r="EF45" s="16">
         <f t="shared" si="2"/>
         <v>1.361057142857143</v>
       </c>
-      <c r="EG45" s="19">
+      <c r="EG45" s="16">
         <f t="shared" si="2"/>
         <v>1.3676285714285714</v>
       </c>
-      <c r="EH45" s="19">
+      <c r="EH45" s="16">
         <f t="shared" si="2"/>
         <v>1.4530857142857143</v>
       </c>
-      <c r="EI45" s="19">
+      <c r="EI45" s="16">
         <f t="shared" si="2"/>
         <v>1.4305000000000001</v>
       </c>
-      <c r="EJ45" s="19">
+      <c r="EJ45" s="16">
         <f t="shared" si="2"/>
         <v>1.4528571428571428</v>
       </c>
-      <c r="EK45" s="19">
+      <c r="EK45" s="16">
         <f t="shared" si="2"/>
         <v>1.4012428571428572</v>
       </c>
-      <c r="EL45" s="19">
+      <c r="EL45" s="16">
         <f t="shared" si="2"/>
         <v>1.3175428571428571</v>
       </c>
-      <c r="EM45" s="19">
+      <c r="EM45" s="16">
         <f t="shared" si="2"/>
         <v>1.3650714285714289</v>
       </c>
-      <c r="EN45" s="19">
+      <c r="EN45" s="16">
         <f t="shared" si="2"/>
         <v>1.4042999999999999</v>
       </c>
-      <c r="EO45" s="19">
+      <c r="EO45" s="16">
         <f t="shared" si="2"/>
         <v>1.3528</v>
       </c>
-      <c r="EP45" s="19">
+      <c r="EP45" s="16">
         <f t="shared" si="2"/>
         <v>1.3242285714285715</v>
       </c>
-      <c r="EQ45" s="19">
+      <c r="EQ45" s="16">
         <f t="shared" si="2"/>
         <v>1.3176428571428571</v>
       </c>
-      <c r="ER45" s="19">
+      <c r="ER45" s="16">
         <f t="shared" si="2"/>
         <v>1.3505285714285713</v>
       </c>
-      <c r="ES45" s="19">
+      <c r="ES45" s="16">
         <f t="shared" si="2"/>
         <v>1.3641142857142856</v>
       </c>
-      <c r="ET45" s="19">
+      <c r="ET45" s="16">
         <f t="shared" si="2"/>
         <v>1.4486285714285714</v>
       </c>
-      <c r="EU45" s="19">
+      <c r="EU45" s="16">
         <f t="shared" si="2"/>
         <v>1.429742857142857</v>
       </c>
-      <c r="EV45" s="19">
+      <c r="EV45" s="16">
         <f t="shared" si="2"/>
         <v>1.4542142857142859</v>
       </c>
-      <c r="EW45" s="19">
+      <c r="EW45" s="16">
         <f t="shared" si="2"/>
         <v>1.4050428571428573</v>
       </c>
-      <c r="EX45" s="19">
+      <c r="EX45" s="16">
         <f t="shared" si="2"/>
         <v>1.3199857142857143</v>
       </c>
-      <c r="EY45" s="19">
+      <c r="EY45" s="16">
         <f t="shared" si="2"/>
         <v>1.3633142857142857</v>
       </c>
-      <c r="EZ45" s="19">
+      <c r="EZ45" s="16">
         <f t="shared" si="2"/>
         <v>1.4002571428571429</v>
       </c>
-      <c r="FA45" s="19">
+      <c r="FA45" s="16">
         <f t="shared" si="2"/>
         <v>1.3501285714285713</v>
       </c>
-      <c r="FB45" s="19">
+      <c r="FB45" s="16">
         <f t="shared" si="2"/>
         <v>1.3207285714285713</v>
       </c>
-      <c r="FC45" s="19">
+      <c r="FC45" s="16">
         <f t="shared" si="2"/>
         <v>1.314942857142857</v>
       </c>
-      <c r="FD45" s="19">
+      <c r="FD45" s="16">
         <f t="shared" si="2"/>
         <v>1.3534857142857142</v>
       </c>
-      <c r="FE45" s="19">
+      <c r="FE45" s="16">
         <f t="shared" si="2"/>
         <v>1.3600857142857143</v>
       </c>
-      <c r="FF45" s="19">
+      <c r="FF45" s="16">
         <f t="shared" si="2"/>
         <v>1.443842857142857</v>
       </c>
-      <c r="FG45" s="19">
+      <c r="FG45" s="16">
         <f t="shared" si="2"/>
         <v>1.4286857142857143</v>
       </c>
-      <c r="FH45" s="19">
+      <c r="FH45" s="16">
         <f t="shared" si="2"/>
         <v>1.4551714285714288</v>
       </c>
-      <c r="FI45" s="19">
+      <c r="FI45" s="16">
         <f t="shared" si="2"/>
         <v>1.4090857142857143</v>
       </c>
-      <c r="FJ45" s="19">
+      <c r="FJ45" s="16">
         <f t="shared" si="2"/>
         <v>1.3222571428571428</v>
       </c>
-      <c r="FK45" s="19">
+      <c r="FK45" s="16">
         <f t="shared" si="2"/>
         <v>1.3618571428571431</v>
       </c>
-      <c r="FL45" s="19">
+      <c r="FL45" s="16">
         <f t="shared" si="2"/>
         <v>1.3977142857142859</v>
       </c>
-      <c r="FM45" s="19">
+      <c r="FM45" s="16">
         <f t="shared" si="2"/>
         <v>1.3473857142857142</v>
       </c>
-      <c r="FN45" s="19">
+      <c r="FN45" s="16">
         <f t="shared" si="2"/>
         <v>1.3193999999999999</v>
       </c>
-      <c r="FO45" s="19">
+      <c r="FO45" s="16">
         <f t="shared" si="2"/>
         <v>1.3116000000000001</v>
       </c>
-      <c r="FP45" s="19">
+      <c r="FP45" s="16">
         <f t="shared" si="2"/>
         <v>1.350657142857143</v>
       </c>
-      <c r="FQ45" s="19">
+      <c r="FQ45" s="16">
         <f t="shared" si="2"/>
         <v>1.3565</v>
       </c>
-      <c r="FR45" s="19">
+      <c r="FR45" s="16">
         <f t="shared" si="2"/>
         <v>1.4395571428571432</v>
       </c>
-      <c r="FS45" s="19">
+      <c r="FS45" s="16">
         <f t="shared" si="2"/>
         <v>1.4276</v>
       </c>
-      <c r="FT45" s="19">
+      <c r="FT45" s="16">
         <f t="shared" si="2"/>
         <v>1.4552714285714285</v>
       </c>
-      <c r="FU45" s="19">
+      <c r="FU45" s="16">
         <f t="shared" si="2"/>
         <v>1.4124714285714286</v>
       </c>
-      <c r="FV45" s="19">
+      <c r="FV45" s="16">
         <f t="shared" si="2"/>
         <v>1.3240714285714286</v>
       </c>
-      <c r="FW45" s="19">
+      <c r="FW45" s="16">
         <f t="shared" si="2"/>
         <v>1.3597999999999999</v>
       </c>
-      <c r="FX45" s="19">
+      <c r="FX45" s="16">
         <f t="shared" si="2"/>
         <v>1.3946571428571428</v>
       </c>
-      <c r="FY45" s="19">
+      <c r="FY45" s="16">
         <f t="shared" si="2"/>
         <v>1.3444</v>
       </c>
@@ -36092,723 +37672,723 @@
       <c r="A46" s="2">
         <v>2</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B46" s="16">
         <f t="shared" ref="B46:BM46" si="3">AVERAGE(B40,B34,B28,B22,B16,B10,B4)</f>
         <v>1.109157142857143</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="16">
         <f t="shared" si="3"/>
         <v>1.098742857142857</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="16">
         <f t="shared" si="3"/>
         <v>1.1235571428571429</v>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="16">
         <f t="shared" si="3"/>
         <v>1.1426714285714286</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="16">
         <f t="shared" si="3"/>
         <v>1.1654714285714285</v>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="16">
         <f t="shared" si="3"/>
         <v>1.1448285714285713</v>
       </c>
-      <c r="H46" s="19">
+      <c r="H46" s="16">
         <f t="shared" si="3"/>
         <v>1.1429000000000002</v>
       </c>
-      <c r="I46" s="19">
+      <c r="I46" s="16">
         <f t="shared" si="3"/>
         <v>1.1484000000000001</v>
       </c>
-      <c r="J46" s="19">
+      <c r="J46" s="16">
         <f t="shared" si="3"/>
         <v>1.1269714285714285</v>
       </c>
-      <c r="K46" s="19">
+      <c r="K46" s="16">
         <f t="shared" si="3"/>
         <v>1.1195285714285714</v>
       </c>
-      <c r="L46" s="19">
+      <c r="L46" s="16">
         <f t="shared" si="3"/>
         <v>1.1201285714285714</v>
       </c>
-      <c r="M46" s="19">
+      <c r="M46" s="16">
         <f t="shared" si="3"/>
         <v>1.1297999999999999</v>
       </c>
-      <c r="N46" s="19">
+      <c r="N46" s="16">
         <f t="shared" si="3"/>
         <v>1.1074857142857142</v>
       </c>
-      <c r="O46" s="19">
+      <c r="O46" s="16">
         <f t="shared" si="3"/>
         <v>1.098257142857143</v>
       </c>
-      <c r="P46" s="19">
+      <c r="P46" s="16">
         <f t="shared" si="3"/>
         <v>1.1303000000000001</v>
       </c>
-      <c r="Q46" s="19">
+      <c r="Q46" s="16">
         <f t="shared" si="3"/>
         <v>1.1443857142857143</v>
       </c>
-      <c r="R46" s="19">
+      <c r="R46" s="16">
         <f t="shared" si="3"/>
         <v>1.1639428571428572</v>
       </c>
-      <c r="S46" s="19">
+      <c r="S46" s="16">
         <f t="shared" si="3"/>
         <v>1.1479571428571429</v>
       </c>
-      <c r="T46" s="19">
+      <c r="T46" s="16">
         <f t="shared" si="3"/>
         <v>1.1472714285714285</v>
       </c>
-      <c r="U46" s="19">
+      <c r="U46" s="16">
         <f t="shared" si="3"/>
         <v>1.1536714285714285</v>
       </c>
-      <c r="V46" s="19">
+      <c r="V46" s="16">
         <f t="shared" si="3"/>
         <v>1.1308714285714285</v>
       </c>
-      <c r="W46" s="19">
+      <c r="W46" s="16">
         <f t="shared" si="3"/>
         <v>1.1222142857142856</v>
       </c>
-      <c r="X46" s="19">
+      <c r="X46" s="16">
         <f t="shared" si="3"/>
         <v>1.1217428571428572</v>
       </c>
-      <c r="Y46" s="19">
+      <c r="Y46" s="16">
         <f t="shared" si="3"/>
         <v>1.1308142857142855</v>
       </c>
-      <c r="Z46" s="19">
+      <c r="Z46" s="16">
         <f t="shared" si="3"/>
         <v>1.1064428571428571</v>
       </c>
-      <c r="AA46" s="19">
+      <c r="AA46" s="16">
         <f t="shared" si="3"/>
         <v>1.1004428571428571</v>
       </c>
-      <c r="AB46" s="19">
+      <c r="AB46" s="16">
         <f t="shared" si="3"/>
         <v>1.1307142857142856</v>
       </c>
-      <c r="AC46" s="19">
+      <c r="AC46" s="16">
         <f t="shared" si="3"/>
         <v>1.1456857142857142</v>
       </c>
-      <c r="AD46" s="19">
+      <c r="AD46" s="16">
         <f t="shared" si="3"/>
         <v>1.1646285714285713</v>
       </c>
-      <c r="AE46" s="19">
+      <c r="AE46" s="16">
         <f t="shared" si="3"/>
         <v>1.1500571428571431</v>
       </c>
-      <c r="AF46" s="19">
+      <c r="AF46" s="16">
         <f t="shared" si="3"/>
         <v>1.1496142857142857</v>
       </c>
-      <c r="AG46" s="19">
+      <c r="AG46" s="16">
         <f t="shared" si="3"/>
         <v>1.1555285714285717</v>
       </c>
-      <c r="AH46" s="19">
+      <c r="AH46" s="16">
         <f t="shared" si="3"/>
         <v>1.1325857142857143</v>
       </c>
-      <c r="AI46" s="19">
+      <c r="AI46" s="16">
         <f t="shared" si="3"/>
         <v>1.1234</v>
       </c>
-      <c r="AJ46" s="19">
+      <c r="AJ46" s="16">
         <f t="shared" si="3"/>
         <v>1.1232714285714285</v>
       </c>
-      <c r="AK46" s="19">
+      <c r="AK46" s="16">
         <f t="shared" si="3"/>
         <v>1.1323000000000001</v>
       </c>
-      <c r="AL46" s="19">
+      <c r="AL46" s="16">
         <f t="shared" si="3"/>
         <v>1.1079571428571426</v>
       </c>
-      <c r="AM46" s="19">
+      <c r="AM46" s="16">
         <f t="shared" si="3"/>
         <v>1.1035428571428572</v>
       </c>
-      <c r="AN46" s="19">
+      <c r="AN46" s="16">
         <f t="shared" si="3"/>
         <v>1.1331714285714285</v>
       </c>
-      <c r="AO46" s="19">
+      <c r="AO46" s="16">
         <f t="shared" si="3"/>
         <v>1.1481285714285714</v>
       </c>
-      <c r="AP46" s="19">
+      <c r="AP46" s="16">
         <f t="shared" si="3"/>
         <v>1.1664714285714286</v>
       </c>
-      <c r="AQ46" s="19">
+      <c r="AQ46" s="16">
         <f t="shared" si="3"/>
         <v>1.1520428571428571</v>
       </c>
-      <c r="AR46" s="19">
+      <c r="AR46" s="16">
         <f t="shared" si="3"/>
         <v>1.1507714285714286</v>
       </c>
-      <c r="AS46" s="19">
+      <c r="AS46" s="16">
         <f t="shared" si="3"/>
         <v>1.156914285714286</v>
       </c>
-      <c r="AT46" s="19">
+      <c r="AT46" s="16">
         <f t="shared" si="3"/>
         <v>1.1340142857142859</v>
       </c>
-      <c r="AU46" s="19">
+      <c r="AU46" s="16">
         <f t="shared" si="3"/>
         <v>1.1248857142857143</v>
       </c>
-      <c r="AV46" s="19">
+      <c r="AV46" s="16">
         <f t="shared" si="3"/>
         <v>1.1256714285714284</v>
       </c>
-      <c r="AW46" s="19">
+      <c r="AW46" s="16">
         <f t="shared" si="3"/>
         <v>1.1345857142857141</v>
       </c>
-      <c r="AX46" s="19">
+      <c r="AX46" s="16">
         <f t="shared" si="3"/>
         <v>1.1094285714285717</v>
       </c>
-      <c r="AY46" s="19">
+      <c r="AY46" s="16">
         <f t="shared" si="3"/>
         <v>1.1104000000000001</v>
       </c>
-      <c r="AZ46" s="19">
+      <c r="AZ46" s="16">
         <f t="shared" si="3"/>
         <v>1.1292714285714285</v>
       </c>
-      <c r="BA46" s="19">
+      <c r="BA46" s="16">
         <f t="shared" si="3"/>
         <v>1.1501714285714286</v>
       </c>
-      <c r="BB46" s="19">
+      <c r="BB46" s="16">
         <f t="shared" si="3"/>
         <v>1.1678285714285714</v>
       </c>
-      <c r="BC46" s="19">
+      <c r="BC46" s="16">
         <f t="shared" si="3"/>
         <v>1.153385714285714</v>
       </c>
-      <c r="BD46" s="19">
+      <c r="BD46" s="16">
         <f t="shared" si="3"/>
         <v>1.1516714285714287</v>
       </c>
-      <c r="BE46" s="19">
+      <c r="BE46" s="16">
         <f t="shared" si="3"/>
         <v>1.1575714285714285</v>
       </c>
-      <c r="BF46" s="19">
+      <c r="BF46" s="16">
         <f t="shared" si="3"/>
         <v>1.1347285714285713</v>
       </c>
-      <c r="BG46" s="19">
+      <c r="BG46" s="16">
         <f t="shared" si="3"/>
         <v>1.1258428571428571</v>
       </c>
-      <c r="BH46" s="19">
+      <c r="BH46" s="16">
         <f t="shared" si="3"/>
         <v>1.1273714285714285</v>
       </c>
-      <c r="BI46" s="19">
+      <c r="BI46" s="16">
         <f t="shared" si="3"/>
         <v>1.1366714285714286</v>
       </c>
-      <c r="BJ46" s="19">
+      <c r="BJ46" s="16">
         <f t="shared" si="3"/>
         <v>1.1116285714285714</v>
       </c>
-      <c r="BK46" s="19">
+      <c r="BK46" s="16">
         <f t="shared" si="3"/>
         <v>1.1084714285714286</v>
       </c>
-      <c r="BL46" s="19">
+      <c r="BL46" s="16">
         <f t="shared" si="3"/>
         <v>1.137342857142857</v>
       </c>
-      <c r="BM46" s="19">
+      <c r="BM46" s="16">
         <f t="shared" si="3"/>
         <v>1.1521142857142856</v>
       </c>
-      <c r="BN46" s="19">
+      <c r="BN46" s="16">
         <f t="shared" ref="BN46:DY46" si="4">AVERAGE(BN40,BN34,BN28,BN22,BN16,BN10,BN4)</f>
         <v>1.1696285714285715</v>
       </c>
-      <c r="BO46" s="19">
+      <c r="BO46" s="16">
         <f t="shared" si="4"/>
         <v>1.1553142857142855</v>
       </c>
-      <c r="BP46" s="19">
+      <c r="BP46" s="16">
         <f t="shared" si="4"/>
         <v>1.1526714285714286</v>
       </c>
-      <c r="BQ46" s="19">
+      <c r="BQ46" s="16">
         <f t="shared" si="4"/>
         <v>1.1580714285714286</v>
       </c>
-      <c r="BR46" s="19">
+      <c r="BR46" s="16">
         <f t="shared" si="4"/>
         <v>1.135542857142857</v>
       </c>
-      <c r="BS46" s="19">
+      <c r="BS46" s="16">
         <f t="shared" si="4"/>
         <v>1.1274571428571429</v>
       </c>
-      <c r="BT46" s="19">
+      <c r="BT46" s="16">
         <f t="shared" si="4"/>
         <v>1.1302857142857143</v>
       </c>
-      <c r="BU46" s="19">
+      <c r="BU46" s="16">
         <f t="shared" si="4"/>
         <v>1.1393</v>
       </c>
-      <c r="BV46" s="19">
+      <c r="BV46" s="16">
         <f t="shared" si="4"/>
         <v>1.1129857142857142</v>
       </c>
-      <c r="BW46" s="19">
+      <c r="BW46" s="16">
         <f t="shared" si="4"/>
         <v>1.1104999999999998</v>
       </c>
-      <c r="BX46" s="19">
+      <c r="BX46" s="16">
         <f t="shared" si="4"/>
         <v>1.1389285714285715</v>
       </c>
-      <c r="BY46" s="19">
+      <c r="BY46" s="16">
         <f t="shared" si="4"/>
         <v>1.1536428571428574</v>
       </c>
-      <c r="BZ46" s="19">
+      <c r="BZ46" s="16">
         <f t="shared" si="4"/>
         <v>1.1708857142857145</v>
       </c>
-      <c r="CA46" s="19">
+      <c r="CA46" s="16">
         <f t="shared" si="4"/>
         <v>1.1569285714285713</v>
       </c>
-      <c r="CB46" s="19">
+      <c r="CB46" s="16">
         <f t="shared" si="4"/>
         <v>1.1536714285714287</v>
       </c>
-      <c r="CC46" s="19">
+      <c r="CC46" s="16">
         <f t="shared" si="4"/>
         <v>1.1585857142857143</v>
       </c>
-      <c r="CD46" s="19">
+      <c r="CD46" s="16">
         <f t="shared" si="4"/>
         <v>1.1361571428571429</v>
       </c>
-      <c r="CE46" s="19">
+      <c r="CE46" s="16">
         <f t="shared" si="4"/>
         <v>1.1285428571428571</v>
       </c>
-      <c r="CF46" s="19">
+      <c r="CF46" s="16">
         <f t="shared" si="4"/>
         <v>1.1320285714285714</v>
       </c>
-      <c r="CG46" s="19">
+      <c r="CG46" s="16">
         <f t="shared" si="4"/>
         <v>1.1411</v>
       </c>
-      <c r="CH46" s="19">
+      <c r="CH46" s="16">
         <f t="shared" si="4"/>
         <v>1.1144571428571428</v>
       </c>
-      <c r="CI46" s="19">
+      <c r="CI46" s="16">
         <f t="shared" si="4"/>
         <v>1.1122999999999998</v>
       </c>
-      <c r="CJ46" s="19">
+      <c r="CJ46" s="16">
         <f t="shared" si="4"/>
         <v>1.1403285714285716</v>
       </c>
-      <c r="CK46" s="19">
+      <c r="CK46" s="16">
         <f t="shared" si="4"/>
         <v>1.1550571428571428</v>
       </c>
-      <c r="CL46" s="19">
+      <c r="CL46" s="16">
         <f t="shared" si="4"/>
         <v>1.1720857142857142</v>
       </c>
-      <c r="CM46" s="19">
+      <c r="CM46" s="16">
         <f t="shared" si="4"/>
         <v>1.1588857142857143</v>
       </c>
-      <c r="CN46" s="19">
+      <c r="CN46" s="16">
         <f t="shared" si="4"/>
         <v>1.1543571428571429</v>
       </c>
-      <c r="CO46" s="19">
+      <c r="CO46" s="16">
         <f t="shared" si="4"/>
         <v>1.1587428571428571</v>
       </c>
-      <c r="CP46" s="19">
+      <c r="CP46" s="16">
         <f t="shared" si="4"/>
         <v>1.1362857142857141</v>
       </c>
-      <c r="CQ46" s="19">
+      <c r="CQ46" s="16">
         <f t="shared" si="4"/>
         <v>1.1293857142857144</v>
       </c>
-      <c r="CR46" s="19">
+      <c r="CR46" s="16">
         <f t="shared" si="4"/>
         <v>1.1335000000000002</v>
       </c>
-      <c r="CS46" s="19">
+      <c r="CS46" s="16">
         <f t="shared" si="4"/>
         <v>1.1422857142857143</v>
       </c>
-      <c r="CT46" s="19">
+      <c r="CT46" s="16">
         <f t="shared" si="4"/>
         <v>1.1158142857142859</v>
       </c>
-      <c r="CU46" s="19">
+      <c r="CU46" s="16">
         <f t="shared" si="4"/>
         <v>1.116842857142857</v>
       </c>
-      <c r="CV46" s="19">
+      <c r="CV46" s="16">
         <f t="shared" si="4"/>
         <v>1.1353285714285715</v>
       </c>
-      <c r="CW46" s="19">
+      <c r="CW46" s="16">
         <f t="shared" si="4"/>
         <v>1.1560571428571429</v>
       </c>
-      <c r="CX46" s="19">
+      <c r="CX46" s="16">
         <f t="shared" si="4"/>
         <v>1.1730714285714285</v>
       </c>
-      <c r="CY46" s="19">
+      <c r="CY46" s="16">
         <f t="shared" si="4"/>
         <v>1.1604285714285716</v>
       </c>
-      <c r="CZ46" s="19">
+      <c r="CZ46" s="16">
         <f t="shared" si="4"/>
         <v>1.1545857142857141</v>
       </c>
-      <c r="DA46" s="19">
+      <c r="DA46" s="16">
         <f t="shared" si="4"/>
         <v>1.1583142857142856</v>
       </c>
-      <c r="DB46" s="19">
+      <c r="DB46" s="16">
         <f t="shared" si="4"/>
         <v>1.1359142857142857</v>
       </c>
-      <c r="DC46" s="19">
+      <c r="DC46" s="16">
         <f t="shared" si="4"/>
         <v>1.1298142857142857</v>
       </c>
-      <c r="DD46" s="19">
+      <c r="DD46" s="16">
         <f t="shared" si="4"/>
         <v>1.1345571428571428</v>
       </c>
-      <c r="DE46" s="19">
+      <c r="DE46" s="16">
         <f t="shared" si="4"/>
         <v>1.1435</v>
       </c>
-      <c r="DF46" s="19">
+      <c r="DF46" s="16">
         <f t="shared" si="4"/>
         <v>1.1158142857142856</v>
       </c>
-      <c r="DG46" s="19">
+      <c r="DG46" s="16">
         <f t="shared" si="4"/>
         <v>1.1132000000000002</v>
       </c>
-      <c r="DH46" s="19">
+      <c r="DH46" s="16">
         <f t="shared" si="4"/>
         <v>1.1415857142857144</v>
       </c>
-      <c r="DI46" s="19">
+      <c r="DI46" s="16">
         <f t="shared" si="4"/>
         <v>1.1562428571428571</v>
       </c>
-      <c r="DJ46" s="19">
+      <c r="DJ46" s="16">
         <f t="shared" si="4"/>
         <v>1.1732857142857145</v>
       </c>
-      <c r="DK46" s="19">
+      <c r="DK46" s="16">
         <f t="shared" si="4"/>
         <v>1.1616714285714287</v>
       </c>
-      <c r="DL46" s="19">
+      <c r="DL46" s="16">
         <f t="shared" si="4"/>
         <v>1.1547857142857143</v>
       </c>
-      <c r="DM46" s="19">
+      <c r="DM46" s="16">
         <f t="shared" si="4"/>
         <v>1.1579285714285714</v>
       </c>
-      <c r="DN46" s="19">
+      <c r="DN46" s="16">
         <f t="shared" si="4"/>
         <v>1.1355428571428572</v>
       </c>
-      <c r="DO46" s="19">
+      <c r="DO46" s="16">
         <f t="shared" si="4"/>
         <v>1.1305000000000001</v>
       </c>
-      <c r="DP46" s="19">
+      <c r="DP46" s="16">
         <f t="shared" si="4"/>
         <v>1.1358571428571429</v>
       </c>
-      <c r="DQ46" s="19">
+      <c r="DQ46" s="16">
         <f t="shared" si="4"/>
         <v>1.1442714285714286</v>
       </c>
-      <c r="DR46" s="19">
+      <c r="DR46" s="16">
         <f t="shared" si="4"/>
         <v>1.1164857142857141</v>
       </c>
-      <c r="DS46" s="19">
+      <c r="DS46" s="16">
         <f t="shared" si="4"/>
         <v>1.1134999999999999</v>
       </c>
-      <c r="DT46" s="19">
+      <c r="DT46" s="16">
         <f t="shared" si="4"/>
         <v>1.1421142857142859</v>
       </c>
-      <c r="DU46" s="19">
+      <c r="DU46" s="16">
         <f t="shared" si="4"/>
         <v>1.1567285714285713</v>
       </c>
-      <c r="DV46" s="19">
+      <c r="DV46" s="16">
         <f t="shared" si="4"/>
         <v>1.1737714285714287</v>
       </c>
-      <c r="DW46" s="19">
+      <c r="DW46" s="16">
         <f t="shared" si="4"/>
         <v>1.1634285714285715</v>
       </c>
-      <c r="DX46" s="19">
+      <c r="DX46" s="16">
         <f t="shared" si="4"/>
         <v>1.1555</v>
       </c>
-      <c r="DY46" s="19">
+      <c r="DY46" s="16">
         <f t="shared" si="4"/>
         <v>1.1578285714285712</v>
       </c>
-      <c r="DZ46" s="19">
+      <c r="DZ46" s="16">
         <f t="shared" ref="DZ46:FY46" si="5">AVERAGE(DZ40,DZ34,DZ28,DZ22,DZ16,DZ10,DZ4)</f>
         <v>1.1355285714285714</v>
       </c>
-      <c r="EA46" s="19">
+      <c r="EA46" s="16">
         <f t="shared" si="5"/>
         <v>1.131342857142857</v>
       </c>
-      <c r="EB46" s="19">
+      <c r="EB46" s="16">
         <f t="shared" si="5"/>
         <v>1.136957142857143</v>
       </c>
-      <c r="EC46" s="19">
+      <c r="EC46" s="16">
         <f t="shared" si="5"/>
         <v>1.1451</v>
       </c>
-      <c r="ED46" s="19">
+      <c r="ED46" s="16">
         <f t="shared" si="5"/>
         <v>1.1170714285714285</v>
       </c>
-      <c r="EE46" s="19">
+      <c r="EE46" s="16">
         <f t="shared" si="5"/>
         <v>1.1137857142857144</v>
       </c>
-      <c r="EF46" s="19">
+      <c r="EF46" s="16">
         <f t="shared" si="5"/>
         <v>1.1425000000000001</v>
       </c>
-      <c r="EG46" s="19">
+      <c r="EG46" s="16">
         <f t="shared" si="5"/>
         <v>1.1570285714285713</v>
       </c>
-      <c r="EH46" s="19">
+      <c r="EH46" s="16">
         <f t="shared" si="5"/>
         <v>1.1743428571428571</v>
       </c>
-      <c r="EI46" s="19">
+      <c r="EI46" s="16">
         <f t="shared" si="5"/>
         <v>1.1651714285714285</v>
       </c>
-      <c r="EJ46" s="19">
+      <c r="EJ46" s="16">
         <f t="shared" si="5"/>
         <v>1.1565285714285716</v>
       </c>
-      <c r="EK46" s="19">
+      <c r="EK46" s="16">
         <f t="shared" si="5"/>
         <v>1.1580999999999999</v>
       </c>
-      <c r="EL46" s="19">
+      <c r="EL46" s="16">
         <f t="shared" si="5"/>
         <v>1.1359142857142857</v>
       </c>
-      <c r="EM46" s="19">
+      <c r="EM46" s="16">
         <f t="shared" si="5"/>
         <v>1.1325000000000001</v>
       </c>
-      <c r="EN46" s="19">
+      <c r="EN46" s="16">
         <f t="shared" si="5"/>
         <v>1.1380999999999999</v>
       </c>
-      <c r="EO46" s="19">
+      <c r="EO46" s="16">
         <f t="shared" si="5"/>
         <v>1.1460428571428571</v>
       </c>
-      <c r="EP46" s="19">
+      <c r="EP46" s="16">
         <f t="shared" si="5"/>
         <v>1.1179857142857141</v>
       </c>
-      <c r="EQ46" s="19">
+      <c r="EQ46" s="16">
         <f t="shared" si="5"/>
         <v>1.1180857142857143</v>
       </c>
-      <c r="ER46" s="19">
+      <c r="ER46" s="16">
         <f t="shared" si="5"/>
         <v>1.1371285714285715</v>
       </c>
-      <c r="ES46" s="19">
+      <c r="ES46" s="16">
         <f t="shared" si="5"/>
         <v>1.1574714285714285</v>
       </c>
-      <c r="ET46" s="19">
+      <c r="ET46" s="16">
         <f t="shared" si="5"/>
         <v>1.1747571428571428</v>
       </c>
-      <c r="EU46" s="19">
+      <c r="EU46" s="16">
         <f t="shared" si="5"/>
         <v>1.209842857142857</v>
       </c>
-      <c r="EV46" s="19">
+      <c r="EV46" s="16">
         <f t="shared" si="5"/>
         <v>1.1578142857142857</v>
       </c>
-      <c r="EW46" s="19">
+      <c r="EW46" s="16">
         <f t="shared" si="5"/>
         <v>1.1583428571428571</v>
       </c>
-      <c r="EX46" s="19">
+      <c r="EX46" s="16">
         <f t="shared" si="5"/>
         <v>1.1364000000000001</v>
       </c>
-      <c r="EY46" s="19">
+      <c r="EY46" s="16">
         <f t="shared" si="5"/>
         <v>1.1333</v>
       </c>
-      <c r="EZ46" s="19">
+      <c r="EZ46" s="16">
         <f t="shared" si="5"/>
         <v>1.1387428571428571</v>
       </c>
-      <c r="FA46" s="19">
+      <c r="FA46" s="16">
         <f t="shared" si="5"/>
         <v>1.1467571428571428</v>
       </c>
-      <c r="FB46" s="19">
+      <c r="FB46" s="16">
         <f t="shared" si="5"/>
         <v>1.1178857142857141</v>
       </c>
-      <c r="FC46" s="19">
+      <c r="FC46" s="16">
         <f t="shared" si="5"/>
         <v>1.1139714285714286</v>
       </c>
-      <c r="FD46" s="19">
+      <c r="FD46" s="16">
         <f t="shared" si="5"/>
         <v>1.1429142857142855</v>
       </c>
-      <c r="FE46" s="19">
+      <c r="FE46" s="16">
         <f t="shared" si="5"/>
         <v>1.1574714285714285</v>
       </c>
-      <c r="FF46" s="19">
+      <c r="FF46" s="16">
         <f t="shared" si="5"/>
         <v>1.1749571428571428</v>
       </c>
-      <c r="FG46" s="19">
+      <c r="FG46" s="16">
         <f t="shared" si="5"/>
         <v>1.1684285714285714</v>
       </c>
-      <c r="FH46" s="19">
+      <c r="FH46" s="16">
         <f t="shared" si="5"/>
         <v>1.1596571428571429</v>
       </c>
-      <c r="FI46" s="19">
+      <c r="FI46" s="16">
         <f t="shared" si="5"/>
         <v>1.1589857142857143</v>
       </c>
-      <c r="FJ46" s="19">
+      <c r="FJ46" s="16">
         <f t="shared" si="5"/>
         <v>1.1374</v>
       </c>
-      <c r="FK46" s="19">
+      <c r="FK46" s="16">
         <f t="shared" si="5"/>
         <v>1.1347428571428571</v>
       </c>
-      <c r="FL46" s="19">
+      <c r="FL46" s="16">
         <f t="shared" si="5"/>
         <v>1.1399571428571431</v>
       </c>
-      <c r="FM46" s="19">
+      <c r="FM46" s="16">
         <f t="shared" si="5"/>
         <v>1.1473285714285715</v>
       </c>
-      <c r="FN46" s="19">
+      <c r="FN46" s="16">
         <f t="shared" si="5"/>
         <v>1.1187</v>
       </c>
-      <c r="FO46" s="19">
+      <c r="FO46" s="16">
         <f t="shared" si="5"/>
         <v>1.1140857142857143</v>
       </c>
-      <c r="FP46" s="19">
+      <c r="FP46" s="16">
         <f t="shared" si="5"/>
         <v>1.1435571428571429</v>
       </c>
-      <c r="FQ46" s="19">
+      <c r="FQ46" s="16">
         <f t="shared" si="5"/>
         <v>1.1576428571428572</v>
       </c>
-      <c r="FR46" s="19">
+      <c r="FR46" s="16">
         <f t="shared" si="5"/>
         <v>1.1752714285714287</v>
       </c>
-      <c r="FS46" s="19">
+      <c r="FS46" s="16">
         <f t="shared" si="5"/>
         <v>1.1700857142857146</v>
       </c>
-      <c r="FT46" s="19">
+      <c r="FT46" s="16">
         <f t="shared" si="5"/>
         <v>1.1614142857142855</v>
       </c>
-      <c r="FU46" s="19">
+      <c r="FU46" s="16">
         <f t="shared" si="5"/>
         <v>1.1605428571428571</v>
       </c>
-      <c r="FV46" s="19">
+      <c r="FV46" s="16">
         <f t="shared" si="5"/>
         <v>1.1387</v>
       </c>
-      <c r="FW46" s="19">
+      <c r="FW46" s="16">
         <f t="shared" si="5"/>
         <v>1.1361428571428571</v>
       </c>
-      <c r="FX46" s="19">
+      <c r="FX46" s="16">
         <f t="shared" si="5"/>
         <v>1.1407571428571428</v>
       </c>
-      <c r="FY46" s="19">
+      <c r="FY46" s="16">
         <f t="shared" si="5"/>
         <v>1.1475714285714285</v>
       </c>
@@ -36817,723 +38397,723 @@
       <c r="A47" s="2">
         <v>3</v>
       </c>
-      <c r="B47" s="19">
+      <c r="B47" s="16">
         <f t="shared" ref="B47:BM47" si="6">AVERAGE(B41,B35,B29,B23,B17,B11,B5)</f>
         <v>0.97465714285714278</v>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="16">
         <f t="shared" si="6"/>
         <v>0.96370000000000011</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="16">
         <f t="shared" si="6"/>
         <v>0.97319999999999995</v>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="16">
         <f t="shared" si="6"/>
         <v>0.95610000000000006</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="16">
         <f t="shared" si="6"/>
         <v>0.96950000000000003</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="16">
         <f t="shared" si="6"/>
         <v>0.9598000000000001</v>
       </c>
-      <c r="H47" s="19">
+      <c r="H47" s="16">
         <f t="shared" si="6"/>
         <v>0.96004285714285698</v>
       </c>
-      <c r="I47" s="19">
+      <c r="I47" s="16">
         <f t="shared" si="6"/>
         <v>0.95834285714285716</v>
       </c>
-      <c r="J47" s="19">
+      <c r="J47" s="16">
         <f t="shared" si="6"/>
         <v>0.96742857142857142</v>
       </c>
-      <c r="K47" s="19">
+      <c r="K47" s="16">
         <f t="shared" si="6"/>
         <v>0.96322857142857132</v>
       </c>
-      <c r="L47" s="19">
+      <c r="L47" s="16">
         <f t="shared" si="6"/>
         <v>0.96640000000000004</v>
       </c>
-      <c r="M47" s="19">
+      <c r="M47" s="16">
         <f t="shared" si="6"/>
         <v>0.97565714285714289</v>
       </c>
-      <c r="N47" s="19">
+      <c r="N47" s="16">
         <f t="shared" si="6"/>
         <v>0.97315714285714294</v>
       </c>
-      <c r="O47" s="19">
+      <c r="O47" s="16">
         <f t="shared" si="6"/>
         <v>0.9717285714285715</v>
       </c>
-      <c r="P47" s="19">
+      <c r="P47" s="16">
         <f t="shared" si="6"/>
         <v>0.96729999999999994</v>
       </c>
-      <c r="Q47" s="19">
+      <c r="Q47" s="16">
         <f t="shared" si="6"/>
         <v>0.95128571428571429</v>
       </c>
-      <c r="R47" s="19">
+      <c r="R47" s="16">
         <f t="shared" si="6"/>
         <v>0.95069999999999999</v>
       </c>
-      <c r="S47" s="19">
+      <c r="S47" s="16">
         <f t="shared" si="6"/>
         <v>0.95761428571428575</v>
       </c>
-      <c r="T47" s="19">
+      <c r="T47" s="16">
         <f t="shared" si="6"/>
         <v>0.95890000000000009</v>
       </c>
-      <c r="U47" s="19">
+      <c r="U47" s="16">
         <f t="shared" si="6"/>
         <v>0.95705714285714283</v>
       </c>
-      <c r="V47" s="19">
+      <c r="V47" s="16">
         <f t="shared" si="6"/>
         <v>0.96817142857142868</v>
       </c>
-      <c r="W47" s="19">
+      <c r="W47" s="16">
         <f t="shared" si="6"/>
         <v>0.9615999999999999</v>
       </c>
-      <c r="X47" s="19">
+      <c r="X47" s="16">
         <f t="shared" si="6"/>
         <v>0.96551428571428566</v>
       </c>
-      <c r="Y47" s="19">
+      <c r="Y47" s="16">
         <f t="shared" si="6"/>
         <v>0.9749000000000001</v>
       </c>
-      <c r="Z47" s="19">
+      <c r="Z47" s="16">
         <f t="shared" si="6"/>
         <v>0.97141428571428567</v>
       </c>
-      <c r="AA47" s="19">
+      <c r="AA47" s="16">
         <f t="shared" si="6"/>
         <v>0.97344285714285694</v>
       </c>
-      <c r="AB47" s="19">
+      <c r="AB47" s="16">
         <f t="shared" si="6"/>
         <v>0.9665285714285714</v>
       </c>
-      <c r="AC47" s="19">
+      <c r="AC47" s="16">
         <f t="shared" si="6"/>
         <v>0.95032857142857152</v>
       </c>
-      <c r="AD47" s="19">
+      <c r="AD47" s="16">
         <f t="shared" si="6"/>
         <v>0.94707142857142845</v>
       </c>
-      <c r="AE47" s="19">
+      <c r="AE47" s="16">
         <f t="shared" si="6"/>
         <v>0.9571428571428573</v>
       </c>
-      <c r="AF47" s="19">
+      <c r="AF47" s="16">
         <f t="shared" si="6"/>
         <v>0.95949999999999991</v>
       </c>
-      <c r="AG47" s="19">
+      <c r="AG47" s="16">
         <f t="shared" si="6"/>
         <v>0.95701428571428582</v>
       </c>
-      <c r="AH47" s="19">
+      <c r="AH47" s="16">
         <f t="shared" si="6"/>
         <v>0.96925714285714282</v>
       </c>
-      <c r="AI47" s="19">
+      <c r="AI47" s="16">
         <f t="shared" si="6"/>
         <v>0.96081428571428573</v>
       </c>
-      <c r="AJ47" s="19">
+      <c r="AJ47" s="16">
         <f t="shared" si="6"/>
         <v>0.96454285714285715</v>
       </c>
-      <c r="AK47" s="19">
+      <c r="AK47" s="16">
         <f t="shared" si="6"/>
         <v>0.97408571428571433</v>
       </c>
-      <c r="AL47" s="19">
+      <c r="AL47" s="16">
         <f t="shared" si="6"/>
         <v>0.97044285714285716</v>
       </c>
-      <c r="AM47" s="19">
+      <c r="AM47" s="16">
         <f t="shared" si="6"/>
         <v>0.97350000000000014</v>
       </c>
-      <c r="AN47" s="19">
+      <c r="AN47" s="16">
         <f t="shared" si="6"/>
         <v>0.96568571428571437</v>
       </c>
-      <c r="AO47" s="19">
+      <c r="AO47" s="16">
         <f t="shared" si="6"/>
         <v>0.94872857142857137</v>
       </c>
-      <c r="AP47" s="19">
+      <c r="AP47" s="16">
         <f t="shared" si="6"/>
         <v>0.94485714285714273</v>
       </c>
-      <c r="AQ47" s="19">
+      <c r="AQ47" s="16">
         <f t="shared" si="6"/>
         <v>0.95638571428571428</v>
       </c>
-      <c r="AR47" s="19">
+      <c r="AR47" s="16">
         <f t="shared" si="6"/>
         <v>0.95899999999999985</v>
       </c>
-      <c r="AS47" s="19">
+      <c r="AS47" s="16">
         <f t="shared" si="6"/>
         <v>0.95637142857142865</v>
       </c>
-      <c r="AT47" s="19">
+      <c r="AT47" s="16">
         <f t="shared" si="6"/>
         <v>0.96950000000000003</v>
       </c>
-      <c r="AU47" s="19">
+      <c r="AU47" s="16">
         <f t="shared" si="6"/>
         <v>0.96008571428571432</v>
       </c>
-      <c r="AV47" s="19">
+      <c r="AV47" s="16">
         <f t="shared" si="6"/>
         <v>0.96312857142857133</v>
       </c>
-      <c r="AW47" s="19">
+      <c r="AW47" s="16">
         <f t="shared" si="6"/>
         <v>0.97302857142857135</v>
       </c>
-      <c r="AX47" s="19">
+      <c r="AX47" s="16">
         <f t="shared" si="6"/>
         <v>0.96912857142857134</v>
       </c>
-      <c r="AY47" s="19">
+      <c r="AY47" s="16">
         <f t="shared" si="6"/>
         <v>0.96729999999999994</v>
       </c>
-      <c r="AZ47" s="19">
+      <c r="AZ47" s="16">
         <f t="shared" si="6"/>
         <v>0.9676285714285715</v>
       </c>
-      <c r="BA47" s="19">
+      <c r="BA47" s="16">
         <f t="shared" si="6"/>
         <v>0.94720000000000015</v>
       </c>
-      <c r="BB47" s="19">
+      <c r="BB47" s="16">
         <f t="shared" si="6"/>
         <v>0.94321428571428567</v>
       </c>
-      <c r="BC47" s="19">
+      <c r="BC47" s="16">
         <f t="shared" si="6"/>
         <v>0.95562857142857138</v>
       </c>
-      <c r="BD47" s="19">
+      <c r="BD47" s="16">
         <f t="shared" si="6"/>
         <v>0.95855714285714277</v>
       </c>
-      <c r="BE47" s="19">
+      <c r="BE47" s="16">
         <f t="shared" si="6"/>
         <v>0.95577142857142849</v>
       </c>
-      <c r="BF47" s="19">
+      <c r="BF47" s="16">
         <f t="shared" si="6"/>
         <v>0.96950000000000003</v>
       </c>
-      <c r="BG47" s="19">
+      <c r="BG47" s="16">
         <f t="shared" si="6"/>
         <v>0.95939999999999992</v>
       </c>
-      <c r="BH47" s="19">
+      <c r="BH47" s="16">
         <f t="shared" si="6"/>
         <v>0.96191428571428583</v>
       </c>
-      <c r="BI47" s="19">
+      <c r="BI47" s="16">
         <f t="shared" si="6"/>
         <v>0.97205714285714273</v>
       </c>
-      <c r="BJ47" s="19">
+      <c r="BJ47" s="16">
         <f t="shared" si="6"/>
         <v>0.96761428571428587</v>
       </c>
-      <c r="BK47" s="19">
+      <c r="BK47" s="16">
         <f t="shared" si="6"/>
         <v>0.97320000000000007</v>
       </c>
-      <c r="BL47" s="19">
+      <c r="BL47" s="16">
         <f t="shared" si="6"/>
         <v>0.96419999999999995</v>
       </c>
-      <c r="BM47" s="19">
+      <c r="BM47" s="16">
         <f t="shared" si="6"/>
         <v>0.94578571428571423</v>
       </c>
-      <c r="BN47" s="19">
+      <c r="BN47" s="16">
         <f t="shared" ref="BN47:DY47" si="7">AVERAGE(BN41,BN35,BN29,BN23,BN17,BN11,BN5)</f>
         <v>0.94162857142857148</v>
       </c>
-      <c r="BO47" s="19">
+      <c r="BO47" s="16">
         <f t="shared" si="7"/>
         <v>0.9546</v>
       </c>
-      <c r="BP47" s="19">
+      <c r="BP47" s="16">
         <f t="shared" si="7"/>
         <v>0.95795714285714273</v>
       </c>
-      <c r="BQ47" s="19">
+      <c r="BQ47" s="16">
         <f t="shared" si="7"/>
         <v>0.95504285714285708</v>
       </c>
-      <c r="BR47" s="19">
+      <c r="BR47" s="16">
         <f t="shared" si="7"/>
         <v>0.96925714285714293</v>
       </c>
-      <c r="BS47" s="19">
+      <c r="BS47" s="16">
         <f t="shared" si="7"/>
         <v>0.95849999999999991</v>
       </c>
-      <c r="BT47" s="19">
+      <c r="BT47" s="16">
         <f t="shared" si="7"/>
         <v>0.96010000000000006</v>
       </c>
-      <c r="BU47" s="19">
+      <c r="BU47" s="16">
         <f t="shared" si="7"/>
         <v>0.97098571428571423</v>
       </c>
-      <c r="BV47" s="19">
+      <c r="BV47" s="16">
         <f t="shared" si="7"/>
         <v>0.9668714285714286</v>
       </c>
-      <c r="BW47" s="19">
+      <c r="BW47" s="16">
         <f t="shared" si="7"/>
         <v>0.97340000000000004</v>
       </c>
-      <c r="BX47" s="19">
+      <c r="BX47" s="16">
         <f t="shared" si="7"/>
         <v>0.96365714285714277</v>
       </c>
-      <c r="BY47" s="19">
+      <c r="BY47" s="16">
         <f t="shared" si="7"/>
         <v>0.94458571428571436</v>
       </c>
-      <c r="BZ47" s="19">
+      <c r="BZ47" s="16">
         <f t="shared" si="7"/>
         <v>0.94020000000000004</v>
       </c>
-      <c r="CA47" s="19">
+      <c r="CA47" s="16">
         <f t="shared" si="7"/>
         <v>0.95344285714285726</v>
       </c>
-      <c r="CB47" s="19">
+      <c r="CB47" s="16">
         <f t="shared" si="7"/>
         <v>0.95731428571428567</v>
       </c>
-      <c r="CC47" s="19">
+      <c r="CC47" s="16">
         <f t="shared" si="7"/>
         <v>0.95428571428571429</v>
       </c>
-      <c r="CD47" s="19">
+      <c r="CD47" s="16">
         <f t="shared" si="7"/>
         <v>0.96919999999999995</v>
       </c>
-      <c r="CE47" s="19">
+      <c r="CE47" s="16">
         <f t="shared" si="7"/>
         <v>0.95781428571428573</v>
       </c>
-      <c r="CF47" s="19">
+      <c r="CF47" s="16">
         <f t="shared" si="7"/>
         <v>0.95874285714285712</v>
       </c>
-      <c r="CG47" s="19">
+      <c r="CG47" s="16">
         <f t="shared" si="7"/>
         <v>0.9703142857142858</v>
       </c>
-      <c r="CH47" s="19">
+      <c r="CH47" s="16">
         <f t="shared" si="7"/>
         <v>0.96601428571428571</v>
       </c>
-      <c r="CI47" s="19">
+      <c r="CI47" s="16">
         <f t="shared" si="7"/>
         <v>0.97337142857142855</v>
       </c>
-      <c r="CJ47" s="19">
+      <c r="CJ47" s="16">
         <f t="shared" si="7"/>
         <v>0.96307142857142847</v>
       </c>
-      <c r="CK47" s="19">
+      <c r="CK47" s="16">
         <f t="shared" si="7"/>
         <v>0.94345714285714277</v>
       </c>
-      <c r="CL47" s="19">
+      <c r="CL47" s="16">
         <f t="shared" si="7"/>
         <v>0.9389142857142857</v>
       </c>
-      <c r="CM47" s="19">
+      <c r="CM47" s="16">
         <f t="shared" si="7"/>
         <v>0.95231428571428567</v>
       </c>
-      <c r="CN47" s="19">
+      <c r="CN47" s="16">
         <f t="shared" si="7"/>
         <v>0.95622857142857143</v>
       </c>
-      <c r="CO47" s="19">
+      <c r="CO47" s="16">
         <f t="shared" si="7"/>
         <v>0.95345714285714289</v>
       </c>
-      <c r="CP47" s="19">
+      <c r="CP47" s="16">
         <f t="shared" si="7"/>
         <v>0.96880000000000011</v>
       </c>
-      <c r="CQ47" s="19">
+      <c r="CQ47" s="16">
         <f t="shared" si="7"/>
         <v>0.95737142857142854</v>
       </c>
-      <c r="CR47" s="19">
+      <c r="CR47" s="16">
         <f t="shared" si="7"/>
         <v>0.95778571428571435</v>
       </c>
-      <c r="CS47" s="19">
+      <c r="CS47" s="16">
         <f t="shared" si="7"/>
         <v>0.96958571428571438</v>
       </c>
-      <c r="CT47" s="19">
+      <c r="CT47" s="16">
         <f t="shared" si="7"/>
         <v>0.96531428571428557</v>
       </c>
-      <c r="CU47" s="19">
+      <c r="CU47" s="16">
         <f t="shared" si="7"/>
         <v>0.96465714285714288</v>
       </c>
-      <c r="CV47" s="19">
+      <c r="CV47" s="16">
         <f t="shared" si="7"/>
         <v>0.9656285714285715</v>
       </c>
-      <c r="CW47" s="19">
+      <c r="CW47" s="16">
         <f t="shared" si="7"/>
         <v>0.9425</v>
       </c>
-      <c r="CX47" s="19">
+      <c r="CX47" s="16">
         <f t="shared" si="7"/>
         <v>0.9381571428571428</v>
       </c>
-      <c r="CY47" s="19">
+      <c r="CY47" s="16">
         <f t="shared" si="7"/>
         <v>0.95087142857142837</v>
       </c>
-      <c r="CZ47" s="19">
+      <c r="CZ47" s="16">
         <f t="shared" si="7"/>
         <v>0.95491428571428572</v>
       </c>
-      <c r="DA47" s="19">
+      <c r="DA47" s="16">
         <f t="shared" si="7"/>
         <v>0.9523571428571429</v>
       </c>
-      <c r="DB47" s="19">
+      <c r="DB47" s="16">
         <f t="shared" si="7"/>
         <v>0.96817142857142857</v>
       </c>
-      <c r="DC47" s="19">
+      <c r="DC47" s="16">
         <f t="shared" si="7"/>
         <v>0.95668571428571436</v>
       </c>
-      <c r="DD47" s="19">
+      <c r="DD47" s="16">
         <f t="shared" si="7"/>
         <v>0.9569428571428571</v>
       </c>
-      <c r="DE47" s="19">
+      <c r="DE47" s="16">
         <f t="shared" si="7"/>
         <v>0.96919999999999995</v>
       </c>
-      <c r="DF47" s="19">
+      <c r="DF47" s="16">
         <f t="shared" si="7"/>
         <v>0.96522857142857155</v>
       </c>
-      <c r="DG47" s="19">
+      <c r="DG47" s="16">
         <f t="shared" si="7"/>
         <v>0.97221428571428581</v>
       </c>
-      <c r="DH47" s="19">
+      <c r="DH47" s="16">
         <f t="shared" si="7"/>
         <v>0.96262857142857139</v>
       </c>
-      <c r="DI47" s="19">
+      <c r="DI47" s="16">
         <f t="shared" si="7"/>
         <v>0.9421571428571428</v>
       </c>
-      <c r="DJ47" s="19">
+      <c r="DJ47" s="16">
         <f t="shared" si="7"/>
         <v>0.93759999999999988</v>
       </c>
-      <c r="DK47" s="19">
+      <c r="DK47" s="16">
         <f t="shared" si="7"/>
         <v>0.94968571428571436</v>
       </c>
-      <c r="DL47" s="19">
+      <c r="DL47" s="16">
         <f t="shared" si="7"/>
         <v>0.95348571428571438</v>
       </c>
-      <c r="DM47" s="19">
+      <c r="DM47" s="16">
         <f t="shared" si="7"/>
         <v>0.95137142857142865</v>
       </c>
-      <c r="DN47" s="19">
+      <c r="DN47" s="16">
         <f t="shared" si="7"/>
         <v>0.96732857142857143</v>
       </c>
-      <c r="DO47" s="19">
+      <c r="DO47" s="16">
         <f t="shared" si="7"/>
         <v>0.95607142857142857</v>
       </c>
-      <c r="DP47" s="19">
+      <c r="DP47" s="16">
         <f t="shared" si="7"/>
         <v>0.95612857142857144</v>
       </c>
-      <c r="DQ47" s="19">
+      <c r="DQ47" s="16">
         <f t="shared" si="7"/>
         <v>0.96888571428571424</v>
       </c>
-      <c r="DR47" s="19">
+      <c r="DR47" s="16">
         <f t="shared" si="7"/>
         <v>0.9649428571428571</v>
       </c>
-      <c r="DS47" s="19">
+      <c r="DS47" s="16">
         <f t="shared" si="7"/>
         <v>0.97175714285714299</v>
       </c>
-      <c r="DT47" s="19">
+      <c r="DT47" s="16">
         <f t="shared" si="7"/>
         <v>0.96254285714285726</v>
       </c>
-      <c r="DU47" s="19">
+      <c r="DU47" s="16">
         <f t="shared" si="7"/>
         <v>0.94158571428571436</v>
       </c>
-      <c r="DV47" s="19">
+      <c r="DV47" s="16">
         <f t="shared" si="7"/>
         <v>0.93704285714285707</v>
       </c>
-      <c r="DW47" s="19">
+      <c r="DW47" s="16">
         <f t="shared" si="7"/>
         <v>0.94852857142857139</v>
       </c>
-      <c r="DX47" s="19">
+      <c r="DX47" s="16">
         <f t="shared" si="7"/>
         <v>0.95178571428571423</v>
       </c>
-      <c r="DY47" s="19">
+      <c r="DY47" s="16">
         <f t="shared" si="7"/>
         <v>0.95015714285714281</v>
       </c>
-      <c r="DZ47" s="19">
+      <c r="DZ47" s="16">
         <f t="shared" ref="DZ47:FY47" si="8">AVERAGE(DZ41,DZ35,DZ29,DZ23,DZ17,DZ11,DZ5)</f>
         <v>0.96645714285714279</v>
       </c>
-      <c r="EA47" s="19">
+      <c r="EA47" s="16">
         <f t="shared" si="8"/>
         <v>0.95544285714285704</v>
       </c>
-      <c r="EB47" s="19">
+      <c r="EB47" s="16">
         <f t="shared" si="8"/>
         <v>0.95551428571428565</v>
       </c>
-      <c r="EC47" s="19">
+      <c r="EC47" s="16">
         <f t="shared" si="8"/>
         <v>0.96854285714285726</v>
       </c>
-      <c r="ED47" s="19">
+      <c r="ED47" s="16">
         <f t="shared" si="8"/>
         <v>0.96472857142857138</v>
       </c>
-      <c r="EE47" s="19">
+      <c r="EE47" s="16">
         <f t="shared" si="8"/>
         <v>0.97118571428571421</v>
       </c>
-      <c r="EF47" s="19">
+      <c r="EF47" s="16">
         <f t="shared" si="8"/>
         <v>0.96237142857142843</v>
       </c>
-      <c r="EG47" s="19">
+      <c r="EG47" s="16">
         <f t="shared" si="8"/>
         <v>0.94102857142857144</v>
       </c>
-      <c r="EH47" s="19">
+      <c r="EH47" s="16">
         <f t="shared" si="8"/>
         <v>0.93658571428571435</v>
       </c>
-      <c r="EI47" s="19">
+      <c r="EI47" s="16">
         <f t="shared" si="8"/>
         <v>0.94739999999999991</v>
       </c>
-      <c r="EJ47" s="19">
+      <c r="EJ47" s="16">
         <f t="shared" si="8"/>
         <v>0.95014285714285696</v>
       </c>
-      <c r="EK47" s="19">
+      <c r="EK47" s="16">
         <f t="shared" si="8"/>
         <v>0.9490142857142857</v>
       </c>
-      <c r="EL47" s="19">
+      <c r="EL47" s="16">
         <f t="shared" si="8"/>
         <v>0.96550000000000025</v>
       </c>
-      <c r="EM47" s="19">
+      <c r="EM47" s="16">
         <f t="shared" si="8"/>
         <v>0.9548714285714287</v>
       </c>
-      <c r="EN47" s="19">
+      <c r="EN47" s="16">
         <f t="shared" si="8"/>
         <v>0.95502857142857145</v>
       </c>
-      <c r="EO47" s="19">
+      <c r="EO47" s="16">
         <f t="shared" si="8"/>
         <v>0.96832857142857143</v>
       </c>
-      <c r="EP47" s="19">
+      <c r="EP47" s="16">
         <f t="shared" si="8"/>
         <v>0.96454285714285704</v>
       </c>
-      <c r="EQ47" s="19">
+      <c r="EQ47" s="16">
         <f t="shared" si="8"/>
         <v>0.96125714285714281</v>
       </c>
-      <c r="ER47" s="19">
+      <c r="ER47" s="16">
         <f t="shared" si="8"/>
         <v>0.96542857142857141</v>
       </c>
-      <c r="ES47" s="19">
+      <c r="ES47" s="16">
         <f t="shared" si="8"/>
         <v>0.94051428571428575</v>
       </c>
-      <c r="ET47" s="19">
+      <c r="ET47" s="16">
         <f t="shared" si="8"/>
         <v>0.93621428571428578</v>
       </c>
-      <c r="EU47" s="19">
+      <c r="EU47" s="16">
         <f t="shared" si="8"/>
         <v>1.0074714285714286</v>
       </c>
-      <c r="EV47" s="19">
+      <c r="EV47" s="16">
         <f t="shared" si="8"/>
         <v>0.94830000000000003</v>
       </c>
-      <c r="EW47" s="19">
+      <c r="EW47" s="16">
         <f t="shared" si="8"/>
         <v>0.94782857142857146</v>
       </c>
-      <c r="EX47" s="19">
+      <c r="EX47" s="16">
         <f t="shared" si="8"/>
         <v>0.96445714285714279</v>
       </c>
-      <c r="EY47" s="19">
+      <c r="EY47" s="16">
         <f t="shared" si="8"/>
         <v>0.95422857142857154</v>
       </c>
-      <c r="EZ47" s="19">
+      <c r="EZ47" s="16">
         <f t="shared" si="8"/>
         <v>0.95478571428571435</v>
       </c>
-      <c r="FA47" s="19">
+      <c r="FA47" s="16">
         <f t="shared" si="8"/>
         <v>0.96827142857142845</v>
       </c>
-      <c r="FB47" s="19">
+      <c r="FB47" s="16">
         <f t="shared" si="8"/>
         <v>0.96460000000000001</v>
       </c>
-      <c r="FC47" s="19">
+      <c r="FC47" s="16">
         <f t="shared" si="8"/>
         <v>0.97005714285714295</v>
       </c>
-      <c r="FD47" s="19">
+      <c r="FD47" s="16">
         <f t="shared" si="8"/>
         <v>0.96230000000000004</v>
       </c>
-      <c r="FE47" s="19">
+      <c r="FE47" s="16">
         <f t="shared" si="8"/>
         <v>0.9403285714285714</v>
       </c>
-      <c r="FF47" s="19">
+      <c r="FF47" s="16">
         <f t="shared" si="8"/>
         <v>0.93592857142857144</v>
       </c>
-      <c r="FG47" s="19">
+      <c r="FG47" s="16">
         <f t="shared" si="8"/>
         <v>0.94540000000000002</v>
       </c>
-      <c r="FH47" s="19">
+      <c r="FH47" s="16">
         <f t="shared" si="8"/>
         <v>0.94662857142857137</v>
       </c>
-      <c r="FI47" s="19">
+      <c r="FI47" s="16">
         <f t="shared" si="8"/>
         <v>0.94639999999999991</v>
       </c>
-      <c r="FJ47" s="19">
+      <c r="FJ47" s="16">
         <f t="shared" si="8"/>
         <v>0.96299999999999997</v>
       </c>
-      <c r="FK47" s="19">
+      <c r="FK47" s="16">
         <f t="shared" si="8"/>
         <v>0.95355714285714288</v>
       </c>
-      <c r="FL47" s="19">
+      <c r="FL47" s="16">
         <f t="shared" si="8"/>
         <v>0.95434285714285727</v>
       </c>
-      <c r="FM47" s="19">
+      <c r="FM47" s="16">
         <f t="shared" si="8"/>
         <v>0.96822857142857133</v>
       </c>
-      <c r="FN47" s="19">
+      <c r="FN47" s="16">
         <f t="shared" si="8"/>
         <v>0.96447142857142865</v>
       </c>
-      <c r="FO47" s="19">
+      <c r="FO47" s="16">
         <f t="shared" si="8"/>
         <v>0.96954285714285715</v>
       </c>
-      <c r="FP47" s="19">
+      <c r="FP47" s="16">
         <f t="shared" si="8"/>
         <v>0.96218571428571431</v>
       </c>
-      <c r="FQ47" s="19">
+      <c r="FQ47" s="16">
         <f t="shared" si="8"/>
         <v>0.94002857142857132</v>
       </c>
-      <c r="FR47" s="19">
+      <c r="FR47" s="16">
         <f t="shared" si="8"/>
         <v>0.93567142857142849</v>
       </c>
-      <c r="FS47" s="19">
+      <c r="FS47" s="16">
         <f t="shared" si="8"/>
         <v>0.94460000000000011</v>
       </c>
-      <c r="FT47" s="19">
+      <c r="FT47" s="16">
         <f t="shared" si="8"/>
         <v>0.94501428571428558</v>
       </c>
-      <c r="FU47" s="19">
+      <c r="FU47" s="16">
         <f t="shared" si="8"/>
         <v>0.94510000000000005</v>
       </c>
-      <c r="FV47" s="19">
+      <c r="FV47" s="16">
         <f t="shared" si="8"/>
         <v>0.96150000000000013</v>
       </c>
-      <c r="FW47" s="19">
+      <c r="FW47" s="16">
         <f t="shared" si="8"/>
         <v>0.95300000000000007</v>
       </c>
-      <c r="FX47" s="19">
+      <c r="FX47" s="16">
         <f t="shared" si="8"/>
         <v>0.95397142857142847</v>
       </c>
-      <c r="FY47" s="19">
+      <c r="FY47" s="16">
         <f t="shared" si="8"/>
         <v>0.96814285714285719</v>
       </c>
@@ -37542,723 +39122,723 @@
       <c r="A48" s="2">
         <v>4</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="16">
         <f t="shared" ref="B48:BM48" si="9">AVERAGE(B42,B36,B30,B24,B18,B12,B6)</f>
         <v>0.79238571428571425</v>
       </c>
-      <c r="C48" s="19">
+      <c r="C48" s="16">
         <f t="shared" si="9"/>
         <v>0.81738571428571427</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="16">
         <f t="shared" si="9"/>
         <v>0.81455714285714287</v>
       </c>
-      <c r="E48" s="19">
+      <c r="E48" s="16">
         <f t="shared" si="9"/>
         <v>0.80061428571428572</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="16">
         <f t="shared" si="9"/>
         <v>0.81702857142857133</v>
       </c>
-      <c r="G48" s="19">
+      <c r="G48" s="16">
         <f t="shared" si="9"/>
         <v>0.82702857142857145</v>
       </c>
-      <c r="H48" s="19">
+      <c r="H48" s="16">
         <f t="shared" si="9"/>
         <v>0.83178571428571424</v>
       </c>
-      <c r="I48" s="19">
+      <c r="I48" s="16">
         <f t="shared" si="9"/>
         <v>0.81592857142857145</v>
       </c>
-      <c r="J48" s="19">
+      <c r="J48" s="16">
         <f t="shared" si="9"/>
         <v>0.83239999999999992</v>
       </c>
-      <c r="K48" s="19">
+      <c r="K48" s="16">
         <f t="shared" si="9"/>
         <v>0.8509714285714286</v>
       </c>
-      <c r="L48" s="19">
+      <c r="L48" s="16">
         <f t="shared" si="9"/>
         <v>0.82431428571428567</v>
       </c>
-      <c r="M48" s="19">
+      <c r="M48" s="16">
         <f t="shared" si="9"/>
         <v>0.8296285714285716</v>
       </c>
-      <c r="N48" s="19">
+      <c r="N48" s="16">
         <f t="shared" si="9"/>
         <v>0.78572857142857144</v>
       </c>
-      <c r="O48" s="19">
+      <c r="O48" s="16">
         <f t="shared" si="9"/>
         <v>0.84484285714285712</v>
       </c>
-      <c r="P48" s="19">
+      <c r="P48" s="16">
         <f t="shared" si="9"/>
         <v>0.80432857142857139</v>
       </c>
-      <c r="Q48" s="19">
+      <c r="Q48" s="16">
         <f t="shared" si="9"/>
         <v>0.79105714285714279</v>
       </c>
-      <c r="R48" s="19">
+      <c r="R48" s="16">
         <f t="shared" si="9"/>
         <v>0.79844285714285712</v>
       </c>
-      <c r="S48" s="19">
+      <c r="S48" s="16">
         <f t="shared" si="9"/>
         <v>0.82818571428571419</v>
       </c>
-      <c r="T48" s="19">
+      <c r="T48" s="16">
         <f t="shared" si="9"/>
         <v>0.83952857142857151</v>
       </c>
-      <c r="U48" s="19">
+      <c r="U48" s="16">
         <f t="shared" si="9"/>
         <v>0.8198714285714287</v>
       </c>
-      <c r="V48" s="19">
+      <c r="V48" s="16">
         <f t="shared" si="9"/>
         <v>0.83641428571428567</v>
       </c>
-      <c r="W48" s="19">
+      <c r="W48" s="16">
         <f t="shared" si="9"/>
         <v>0.84964285714285714</v>
       </c>
-      <c r="X48" s="19">
+      <c r="X48" s="16">
         <f t="shared" si="9"/>
         <v>0.82274285714285711</v>
       </c>
-      <c r="Y48" s="19">
+      <c r="Y48" s="16">
         <f t="shared" si="9"/>
         <v>0.82734285714285716</v>
       </c>
-      <c r="Z48" s="19">
+      <c r="Z48" s="16">
         <f t="shared" si="9"/>
         <v>0.78127142857142851</v>
       </c>
-      <c r="AA48" s="19">
+      <c r="AA48" s="16">
         <f t="shared" si="9"/>
         <v>0.85157142857142865</v>
       </c>
-      <c r="AB48" s="19">
+      <c r="AB48" s="16">
         <f t="shared" si="9"/>
         <v>0.80484285714285719</v>
       </c>
-      <c r="AC48" s="19">
+      <c r="AC48" s="16">
         <f t="shared" si="9"/>
         <v>0.79144285714285723</v>
       </c>
-      <c r="AD48" s="19">
+      <c r="AD48" s="16">
         <f t="shared" si="9"/>
         <v>0.79404285714285716</v>
       </c>
-      <c r="AE48" s="19">
+      <c r="AE48" s="16">
         <f t="shared" si="9"/>
         <v>0.83002857142857145</v>
       </c>
-      <c r="AF48" s="19">
+      <c r="AF48" s="16">
         <f t="shared" si="9"/>
         <v>0.84525714285714282</v>
       </c>
-      <c r="AG48" s="19">
+      <c r="AG48" s="16">
         <f t="shared" si="9"/>
         <v>0.82402857142857144</v>
       </c>
-      <c r="AH48" s="19">
+      <c r="AH48" s="16">
         <f t="shared" si="9"/>
         <v>0.8409428571428571</v>
       </c>
-      <c r="AI48" s="19">
+      <c r="AI48" s="16">
         <f t="shared" si="9"/>
         <v>0.85031428571428569</v>
       </c>
-      <c r="AJ48" s="19">
+      <c r="AJ48" s="16">
         <f t="shared" si="9"/>
         <v>0.82157142857142851</v>
       </c>
-      <c r="AK48" s="19">
+      <c r="AK48" s="16">
         <f t="shared" si="9"/>
         <v>0.82550000000000001</v>
       </c>
-      <c r="AL48" s="19">
+      <c r="AL48" s="16">
         <f t="shared" si="9"/>
         <v>0.77714285714285702</v>
       </c>
-      <c r="AM48" s="19">
+      <c r="AM48" s="16">
         <f t="shared" si="9"/>
         <v>0.84854285714285727</v>
       </c>
-      <c r="AN48" s="19">
+      <c r="AN48" s="16">
         <f t="shared" si="9"/>
         <v>0.80067142857142859</v>
       </c>
-      <c r="AO48" s="19">
+      <c r="AO48" s="16">
         <f t="shared" si="9"/>
         <v>0.78591428571428545</v>
       </c>
-      <c r="AP48" s="19">
+      <c r="AP48" s="16">
         <f t="shared" si="9"/>
         <v>0.78848571428571435</v>
       </c>
-      <c r="AQ48" s="19">
+      <c r="AQ48" s="16">
         <f t="shared" si="9"/>
         <v>0.82682857142857136</v>
       </c>
-      <c r="AR48" s="19">
+      <c r="AR48" s="16">
         <f t="shared" si="9"/>
         <v>0.84321428571428569</v>
       </c>
-      <c r="AS48" s="19">
+      <c r="AS48" s="16">
         <f t="shared" si="9"/>
         <v>0.82181428571428583</v>
       </c>
-      <c r="AT48" s="19">
+      <c r="AT48" s="16">
         <f t="shared" si="9"/>
         <v>0.84095714285714285</v>
       </c>
-      <c r="AU48" s="19">
+      <c r="AU48" s="16">
         <f t="shared" si="9"/>
         <v>0.84902857142857158</v>
       </c>
-      <c r="AV48" s="19">
+      <c r="AV48" s="16">
         <f t="shared" si="9"/>
         <v>0.81821428571428567</v>
       </c>
-      <c r="AW48" s="19">
+      <c r="AW48" s="16">
         <f t="shared" si="9"/>
         <v>0.82168571428571435</v>
       </c>
-      <c r="AX48" s="19">
+      <c r="AX48" s="16">
         <f t="shared" si="9"/>
         <v>0.77299999999999991</v>
       </c>
-      <c r="AY48" s="19">
+      <c r="AY48" s="16">
         <f t="shared" si="9"/>
         <v>0.8348714285714286</v>
       </c>
-      <c r="AZ48" s="19">
+      <c r="AZ48" s="16">
         <f t="shared" si="9"/>
         <v>0.80305714285714291</v>
       </c>
-      <c r="BA48" s="19">
+      <c r="BA48" s="16">
         <f t="shared" si="9"/>
         <v>0.77969999999999995</v>
       </c>
-      <c r="BB48" s="19">
+      <c r="BB48" s="16">
         <f t="shared" si="9"/>
         <v>0.78381428571428569</v>
       </c>
-      <c r="BC48" s="19">
+      <c r="BC48" s="16">
         <f t="shared" si="9"/>
         <v>0.82394285714285709</v>
       </c>
-      <c r="BD48" s="19">
+      <c r="BD48" s="16">
         <f t="shared" si="9"/>
         <v>0.84117142857142857</v>
       </c>
-      <c r="BE48" s="19">
+      <c r="BE48" s="16">
         <f t="shared" si="9"/>
         <v>0.81904285714285729</v>
       </c>
-      <c r="BF48" s="19">
+      <c r="BF48" s="16">
         <f t="shared" si="9"/>
         <v>0.84037142857142855</v>
       </c>
-      <c r="BG48" s="19">
+      <c r="BG48" s="16">
         <f t="shared" si="9"/>
         <v>0.84804285714285732</v>
       </c>
-      <c r="BH48" s="19">
+      <c r="BH48" s="16">
         <f t="shared" si="9"/>
         <v>0.81577142857142848</v>
       </c>
-      <c r="BI48" s="19">
+      <c r="BI48" s="16">
         <f t="shared" si="9"/>
         <v>0.81850000000000012</v>
       </c>
-      <c r="BJ48" s="19">
+      <c r="BJ48" s="16">
         <f t="shared" si="9"/>
         <v>0.76814285714285713</v>
       </c>
-      <c r="BK48" s="19">
+      <c r="BK48" s="16">
         <f t="shared" si="9"/>
         <v>0.84065714285714288</v>
       </c>
-      <c r="BL48" s="19">
+      <c r="BL48" s="16">
         <f t="shared" si="9"/>
         <v>0.79182857142857144</v>
       </c>
-      <c r="BM48" s="19">
+      <c r="BM48" s="16">
         <f t="shared" si="9"/>
         <v>0.77397142857142853</v>
       </c>
-      <c r="BN48" s="19">
+      <c r="BN48" s="16">
         <f t="shared" ref="BN48:DY48" si="10">AVERAGE(BN42,BN36,BN30,BN24,BN18,BN12,BN6)</f>
         <v>0.77944285714285699</v>
       </c>
-      <c r="BO48" s="19">
+      <c r="BO48" s="16">
         <f t="shared" si="10"/>
         <v>0.81954285714285713</v>
       </c>
-      <c r="BP48" s="19">
+      <c r="BP48" s="16">
         <f t="shared" si="10"/>
         <v>0.83881428571428585</v>
       </c>
-      <c r="BQ48" s="19">
+      <c r="BQ48" s="16">
         <f t="shared" si="10"/>
         <v>0.81592857142857134</v>
       </c>
-      <c r="BR48" s="19">
+      <c r="BR48" s="16">
         <f t="shared" si="10"/>
         <v>0.83917142857142857</v>
       </c>
-      <c r="BS48" s="19">
+      <c r="BS48" s="16">
         <f t="shared" si="10"/>
         <v>0.8459000000000001</v>
       </c>
-      <c r="BT48" s="19">
+      <c r="BT48" s="16">
         <f t="shared" si="10"/>
         <v>0.81102857142857143</v>
       </c>
-      <c r="BU48" s="19">
+      <c r="BU48" s="16">
         <f t="shared" si="10"/>
         <v>0.81424285714285716</v>
       </c>
-      <c r="BV48" s="19">
+      <c r="BV48" s="16">
         <f t="shared" si="10"/>
         <v>0.76534285714285721</v>
       </c>
-      <c r="BW48" s="19">
+      <c r="BW48" s="16">
         <f t="shared" si="10"/>
         <v>0.83827142857142856</v>
       </c>
-      <c r="BX48" s="19">
+      <c r="BX48" s="16">
         <f t="shared" si="10"/>
         <v>0.78860000000000008</v>
       </c>
-      <c r="BY48" s="19">
+      <c r="BY48" s="16">
         <f t="shared" si="10"/>
         <v>0.76857142857142857</v>
       </c>
-      <c r="BZ48" s="19">
+      <c r="BZ48" s="16">
         <f t="shared" si="10"/>
         <v>0.77549999999999997</v>
       </c>
-      <c r="CA48" s="19">
+      <c r="CA48" s="16">
         <f t="shared" si="10"/>
         <v>0.81552857142857138</v>
       </c>
-      <c r="CB48" s="19">
+      <c r="CB48" s="16">
         <f t="shared" si="10"/>
         <v>0.83661428571428575</v>
       </c>
-      <c r="CC48" s="19">
+      <c r="CC48" s="16">
         <f t="shared" si="10"/>
         <v>0.81328571428571428</v>
       </c>
-      <c r="CD48" s="19">
+      <c r="CD48" s="16">
         <f t="shared" si="10"/>
         <v>0.83892857142857147</v>
       </c>
-      <c r="CE48" s="19">
+      <c r="CE48" s="16">
         <f t="shared" si="10"/>
         <v>0.84472857142857161</v>
       </c>
-      <c r="CF48" s="19">
+      <c r="CF48" s="16">
         <f t="shared" si="10"/>
         <v>0.80795714285714282</v>
       </c>
-      <c r="CG48" s="19">
+      <c r="CG48" s="16">
         <f t="shared" si="10"/>
         <v>0.81135714285714289</v>
       </c>
-      <c r="CH48" s="19">
+      <c r="CH48" s="16">
         <f t="shared" si="10"/>
         <v>0.76194285714285714</v>
       </c>
-      <c r="CI48" s="19">
+      <c r="CI48" s="16">
         <f t="shared" si="10"/>
         <v>0.8352857142857143</v>
       </c>
-      <c r="CJ48" s="19">
+      <c r="CJ48" s="16">
         <f t="shared" si="10"/>
         <v>0.78508571428571439</v>
       </c>
-      <c r="CK48" s="19">
+      <c r="CK48" s="16">
         <f t="shared" si="10"/>
         <v>0.7639285714285714</v>
       </c>
-      <c r="CL48" s="19">
+      <c r="CL48" s="16">
         <f t="shared" si="10"/>
         <v>0.77179999999999993</v>
       </c>
-      <c r="CM48" s="19">
+      <c r="CM48" s="16">
         <f t="shared" si="10"/>
         <v>0.81105714285714281</v>
       </c>
-      <c r="CN48" s="19">
+      <c r="CN48" s="16">
         <f t="shared" si="10"/>
         <v>0.83295714285714306</v>
       </c>
-      <c r="CO48" s="19">
+      <c r="CO48" s="16">
         <f t="shared" si="10"/>
         <v>0.80965714285714274</v>
       </c>
-      <c r="CP48" s="19">
+      <c r="CP48" s="16">
         <f t="shared" si="10"/>
         <v>0.83814285714285719</v>
       </c>
-      <c r="CQ48" s="19">
+      <c r="CQ48" s="16">
         <f t="shared" si="10"/>
         <v>0.84370000000000012</v>
       </c>
-      <c r="CR48" s="19">
+      <c r="CR48" s="16">
         <f t="shared" si="10"/>
         <v>0.80535714285714288</v>
       </c>
-      <c r="CS48" s="19">
+      <c r="CS48" s="16">
         <f t="shared" si="10"/>
         <v>0.80871428571428583</v>
       </c>
-      <c r="CT48" s="19">
+      <c r="CT48" s="16">
         <f t="shared" si="10"/>
         <v>0.7591714285714285</v>
       </c>
-      <c r="CU48" s="19">
+      <c r="CU48" s="16">
         <f t="shared" si="10"/>
         <v>0.82011428571428557</v>
       </c>
-      <c r="CV48" s="19">
+      <c r="CV48" s="16">
         <f t="shared" si="10"/>
         <v>0.78889999999999993</v>
       </c>
-      <c r="CW48" s="19">
+      <c r="CW48" s="16">
         <f t="shared" si="10"/>
         <v>0.75945714285714294</v>
       </c>
-      <c r="CX48" s="19">
+      <c r="CX48" s="16">
         <f t="shared" si="10"/>
         <v>0.76921428571428574</v>
       </c>
-      <c r="CY48" s="19">
+      <c r="CY48" s="16">
         <f t="shared" si="10"/>
         <v>0.80582857142857145</v>
       </c>
-      <c r="CZ48" s="19">
+      <c r="CZ48" s="16">
         <f t="shared" si="10"/>
         <v>0.8285285714285715</v>
       </c>
-      <c r="DA48" s="19">
+      <c r="DA48" s="16">
         <f t="shared" si="10"/>
         <v>0.80451428571428585</v>
       </c>
-      <c r="DB48" s="19">
+      <c r="DB48" s="16">
         <f t="shared" si="10"/>
         <v>0.83732857142857142</v>
       </c>
-      <c r="DC48" s="19">
+      <c r="DC48" s="16">
         <f t="shared" si="10"/>
         <v>0.84248571428571428</v>
       </c>
-      <c r="DD48" s="19">
+      <c r="DD48" s="16">
         <f t="shared" si="10"/>
         <v>0.8031571428571429</v>
       </c>
-      <c r="DE48" s="19">
+      <c r="DE48" s="16">
         <f t="shared" si="10"/>
         <v>0.80645714285714298</v>
       </c>
-      <c r="DF48" s="19">
+      <c r="DF48" s="16">
         <f t="shared" si="10"/>
         <v>0.75872857142857142</v>
       </c>
-      <c r="DG48" s="19">
+      <c r="DG48" s="16">
         <f t="shared" si="10"/>
         <v>0.83000000000000007</v>
       </c>
-      <c r="DH48" s="19">
+      <c r="DH48" s="16">
         <f t="shared" si="10"/>
         <v>0.78077142857142867</v>
       </c>
-      <c r="DI48" s="19">
+      <c r="DI48" s="16">
         <f t="shared" si="10"/>
         <v>0.75682857142857141</v>
       </c>
-      <c r="DJ48" s="19">
+      <c r="DJ48" s="16">
         <f t="shared" si="10"/>
         <v>0.76714285714285713</v>
       </c>
-      <c r="DK48" s="19">
+      <c r="DK48" s="16">
         <f t="shared" si="10"/>
         <v>0.80097142857142856</v>
       </c>
-      <c r="DL48" s="19">
+      <c r="DL48" s="16">
         <f t="shared" si="10"/>
         <v>0.82340000000000002</v>
       </c>
-      <c r="DM48" s="19">
+      <c r="DM48" s="16">
         <f t="shared" si="10"/>
         <v>0.79972857142857134</v>
       </c>
-      <c r="DN48" s="19">
+      <c r="DN48" s="16">
         <f t="shared" si="10"/>
         <v>0.83599999999999997</v>
       </c>
-      <c r="DO48" s="19">
+      <c r="DO48" s="16">
         <f t="shared" si="10"/>
         <v>0.8407714285714285</v>
       </c>
-      <c r="DP48" s="19">
+      <c r="DP48" s="16">
         <f t="shared" si="10"/>
         <v>0.80011428571428578</v>
       </c>
-      <c r="DQ48" s="19">
+      <c r="DQ48" s="16">
         <f t="shared" si="10"/>
         <v>0.80428571428571427</v>
       </c>
-      <c r="DR48" s="19">
+      <c r="DR48" s="16">
         <f t="shared" si="10"/>
         <v>0.75695714285714288</v>
       </c>
-      <c r="DS48" s="19">
+      <c r="DS48" s="16">
         <f t="shared" si="10"/>
         <v>0.82747142857142852</v>
       </c>
-      <c r="DT48" s="19">
+      <c r="DT48" s="16">
         <f t="shared" si="10"/>
         <v>0.77867142857142846</v>
       </c>
-      <c r="DU48" s="19">
+      <c r="DU48" s="16">
         <f t="shared" si="10"/>
         <v>0.75330000000000008</v>
       </c>
-      <c r="DV48" s="19">
+      <c r="DV48" s="16">
         <f t="shared" si="10"/>
         <v>0.7649285714285714</v>
       </c>
-      <c r="DW48" s="19">
+      <c r="DW48" s="16">
         <f t="shared" si="10"/>
         <v>0.79572857142857145</v>
       </c>
-      <c r="DX48" s="19">
+      <c r="DX48" s="16">
         <f t="shared" si="10"/>
         <v>0.8158428571428572</v>
       </c>
-      <c r="DY48" s="19">
+      <c r="DY48" s="16">
         <f t="shared" si="10"/>
         <v>0.79419999999999991</v>
       </c>
-      <c r="DZ48" s="19">
+      <c r="DZ48" s="16">
         <f t="shared" ref="DZ48:FY48" si="11">AVERAGE(DZ42,DZ36,DZ30,DZ24,DZ18,DZ12,DZ6)</f>
         <v>0.8344571428571429</v>
       </c>
-      <c r="EA48" s="19">
+      <c r="EA48" s="16">
         <f t="shared" si="11"/>
         <v>0.83865714285714277</v>
       </c>
-      <c r="EB48" s="19">
+      <c r="EB48" s="16">
         <f t="shared" si="11"/>
         <v>0.79725714285714278</v>
       </c>
-      <c r="EC48" s="19">
+      <c r="EC48" s="16">
         <f t="shared" si="11"/>
         <v>0.80177142857142858</v>
       </c>
-      <c r="ED48" s="19">
+      <c r="ED48" s="16">
         <f t="shared" si="11"/>
         <v>0.75542857142857134</v>
       </c>
-      <c r="EE48" s="19">
+      <c r="EE48" s="16">
         <f t="shared" si="11"/>
         <v>0.8248428571428571</v>
       </c>
-      <c r="EF48" s="19">
+      <c r="EF48" s="16">
         <f t="shared" si="11"/>
         <v>0.77654285714285709</v>
       </c>
-      <c r="EG48" s="19">
+      <c r="EG48" s="16">
         <f t="shared" si="11"/>
         <v>0.75011428571428573</v>
       </c>
-      <c r="EH48" s="19">
+      <c r="EH48" s="16">
         <f t="shared" si="11"/>
         <v>0.76265714285714281</v>
       </c>
-      <c r="EI48" s="19">
+      <c r="EI48" s="16">
         <f t="shared" si="11"/>
         <v>0.79075714285714305</v>
       </c>
-      <c r="EJ48" s="19">
+      <c r="EJ48" s="16">
         <f t="shared" si="11"/>
         <v>0.80865714285714285</v>
       </c>
-      <c r="EK48" s="19">
+      <c r="EK48" s="16">
         <f t="shared" si="11"/>
         <v>0.78901428571428578</v>
       </c>
-      <c r="EL48" s="19">
+      <c r="EL48" s="16">
         <f t="shared" si="11"/>
         <v>0.83248571428571427</v>
       </c>
-      <c r="EM48" s="19">
+      <c r="EM48" s="16">
         <f t="shared" si="11"/>
         <v>0.83625714285714281</v>
       </c>
-      <c r="EN48" s="19">
+      <c r="EN48" s="16">
         <f t="shared" si="11"/>
         <v>0.79470000000000007</v>
       </c>
-      <c r="EO48" s="19">
+      <c r="EO48" s="16">
         <f t="shared" si="11"/>
         <v>0.79964285714285732</v>
       </c>
-      <c r="EP48" s="19">
+      <c r="EP48" s="16">
         <f t="shared" si="11"/>
         <v>0.7535142857142858</v>
       </c>
-      <c r="EQ48" s="19">
+      <c r="EQ48" s="16">
         <f t="shared" si="11"/>
         <v>0.8046714285714287</v>
       </c>
-      <c r="ER48" s="19">
+      <c r="ER48" s="16">
         <f t="shared" si="11"/>
         <v>0.78062857142857145</v>
       </c>
-      <c r="ES48" s="19">
+      <c r="ES48" s="16">
         <f t="shared" si="11"/>
         <v>0.74675714285714279</v>
       </c>
-      <c r="ET48" s="19">
+      <c r="ET48" s="16">
         <f t="shared" si="11"/>
         <v>0.7605857142857142</v>
       </c>
-      <c r="EU48" s="19">
+      <c r="EU48" s="16">
         <f t="shared" si="11"/>
         <v>0.85780000000000012</v>
       </c>
-      <c r="EV48" s="19">
+      <c r="EV48" s="16">
         <f t="shared" si="11"/>
         <v>0.79991428571428558</v>
       </c>
-      <c r="EW48" s="19">
+      <c r="EW48" s="16">
         <f t="shared" si="11"/>
         <v>0.78468571428571432</v>
       </c>
-      <c r="EX48" s="19">
+      <c r="EX48" s="16">
         <f t="shared" si="11"/>
         <v>0.83050000000000002</v>
       </c>
-      <c r="EY48" s="19">
+      <c r="EY48" s="16">
         <f t="shared" si="11"/>
         <v>0.83397142857142847</v>
       </c>
-      <c r="EZ48" s="19">
+      <c r="EZ48" s="16">
         <f t="shared" si="11"/>
         <v>0.79267142857142858</v>
       </c>
-      <c r="FA48" s="19">
+      <c r="FA48" s="16">
         <f t="shared" si="11"/>
         <v>0.79749999999999999</v>
       </c>
-      <c r="FB48" s="19">
+      <c r="FB48" s="16">
         <f t="shared" si="11"/>
         <v>0.75257142857142856</v>
       </c>
-      <c r="FC48" s="19">
+      <c r="FC48" s="16">
         <f t="shared" si="11"/>
         <v>0.81915714285714281</v>
       </c>
-      <c r="FD48" s="19">
+      <c r="FD48" s="16">
         <f t="shared" si="11"/>
         <v>0.7725142857142856</v>
       </c>
-      <c r="FE48" s="19">
+      <c r="FE48" s="16">
         <f t="shared" si="11"/>
         <v>0.74434285714285708</v>
       </c>
-      <c r="FF48" s="19">
+      <c r="FF48" s="16">
         <f t="shared" si="11"/>
         <v>0.75851428571428581</v>
       </c>
-      <c r="FG48" s="19">
+      <c r="FG48" s="16">
         <f t="shared" si="11"/>
         <v>0.78084285714285706</v>
       </c>
-      <c r="FH48" s="19">
+      <c r="FH48" s="16">
         <f t="shared" si="11"/>
         <v>0.79139999999999999</v>
       </c>
-      <c r="FI48" s="19">
+      <c r="FI48" s="16">
         <f t="shared" si="11"/>
         <v>0.77921428571428553</v>
       </c>
-      <c r="FJ48" s="19">
+      <c r="FJ48" s="16">
         <f t="shared" si="11"/>
         <v>0.82705714285714282</v>
       </c>
-      <c r="FK48" s="19">
+      <c r="FK48" s="16">
         <f t="shared" si="11"/>
         <v>0.83071428571428574</v>
       </c>
-      <c r="FL48" s="19">
+      <c r="FL48" s="16">
         <f t="shared" si="11"/>
         <v>0.78945714285714275</v>
       </c>
-      <c r="FM48" s="19">
+      <c r="FM48" s="16">
         <f t="shared" si="11"/>
         <v>0.79530000000000001</v>
       </c>
-      <c r="FN48" s="19">
+      <c r="FN48" s="16">
         <f t="shared" si="11"/>
         <v>0.74970000000000003</v>
       </c>
-      <c r="FO48" s="19">
+      <c r="FO48" s="16">
         <f t="shared" si="11"/>
         <v>0.81650000000000011</v>
       </c>
-      <c r="FP48" s="19">
+      <c r="FP48" s="16">
         <f t="shared" si="11"/>
         <v>0.76962857142857133</v>
       </c>
-      <c r="FQ48" s="19">
+      <c r="FQ48" s="16">
         <f t="shared" si="11"/>
         <v>0.74161428571428567</v>
       </c>
-      <c r="FR48" s="19">
+      <c r="FR48" s="16">
         <f t="shared" si="11"/>
         <v>0.75659999999999994</v>
       </c>
-      <c r="FS48" s="19">
+      <c r="FS48" s="16">
         <f t="shared" si="11"/>
         <v>0.77660000000000007</v>
       </c>
-      <c r="FT48" s="19">
+      <c r="FT48" s="16">
         <f t="shared" si="11"/>
         <v>0.78368571428571432</v>
       </c>
-      <c r="FU48" s="19">
+      <c r="FU48" s="16">
         <f t="shared" si="11"/>
         <v>0.77518571428571448</v>
       </c>
-      <c r="FV48" s="19">
+      <c r="FV48" s="16">
         <f t="shared" si="11"/>
         <v>0.82351428571428564</v>
       </c>
-      <c r="FW48" s="19">
+      <c r="FW48" s="16">
         <f t="shared" si="11"/>
         <v>0.82758571428571426</v>
       </c>
-      <c r="FX48" s="19">
+      <c r="FX48" s="16">
         <f t="shared" si="11"/>
         <v>0.78648571428571423</v>
       </c>
-      <c r="FY48" s="19">
+      <c r="FY48" s="16">
         <f t="shared" si="11"/>
         <v>0.79359999999999986</v>
       </c>
@@ -41056,16 +42636,16 @@
       <c r="H58" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I58" s="17">
+      <c r="I58" s="15">
         <v>1.3517428571428571</v>
       </c>
-      <c r="J58" s="17">
+      <c r="J58" s="15">
         <v>1.1310130952380952</v>
       </c>
-      <c r="K58" s="17">
+      <c r="K58" s="15">
         <v>0.96567142857142851</v>
       </c>
-      <c r="L58" s="17">
+      <c r="L58" s="15">
         <v>0.82116904761904763</v>
       </c>
     </row>
@@ -41088,16 +42668,16 @@
       <c r="H59" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I59" s="17">
+      <c r="I59" s="15">
         <v>1.3648119047619049</v>
       </c>
-      <c r="J59" s="17">
+      <c r="J59" s="15">
         <v>1.133242857142857</v>
       </c>
-      <c r="K59" s="17">
+      <c r="K59" s="15">
         <v>0.96316071428571426</v>
       </c>
-      <c r="L59" s="17">
+      <c r="L59" s="15">
         <v>0.82067738095238107</v>
       </c>
     </row>
@@ -41120,16 +42700,16 @@
       <c r="H60" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I60" s="17">
+      <c r="I60" s="15">
         <v>1.3713166666666667</v>
       </c>
-      <c r="J60" s="17">
+      <c r="J60" s="15">
         <v>1.1345559523809523</v>
       </c>
-      <c r="K60" s="17">
+      <c r="K60" s="15">
         <v>0.96259523809523817</v>
       </c>
-      <c r="L60" s="17">
+      <c r="L60" s="15">
         <v>0.82173452380952383</v>
       </c>
     </row>
@@ -41152,16 +42732,16 @@
       <c r="H61" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="I61" s="17">
+      <c r="I61" s="15">
         <v>1.3752976190476189</v>
       </c>
-      <c r="J61" s="17">
+      <c r="J61" s="15">
         <v>1.1365130952380953</v>
       </c>
-      <c r="K61" s="17">
+      <c r="K61" s="15">
         <v>0.96172619047619046</v>
       </c>
-      <c r="L61" s="17">
+      <c r="L61" s="15">
         <v>0.8185416666666665</v>
       </c>
     </row>
@@ -41184,16 +42764,16 @@
       <c r="H62" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="I62" s="17">
+      <c r="I62" s="15">
         <v>1.3775416666666667</v>
       </c>
-      <c r="J62" s="17">
+      <c r="J62" s="15">
         <v>1.1378619047619047</v>
       </c>
-      <c r="K62" s="17">
+      <c r="K62" s="15">
         <v>0.9606083333333334</v>
       </c>
-      <c r="L62" s="17">
+      <c r="L62" s="15">
         <v>0.81510714285714281</v>
       </c>
     </row>
@@ -41216,16 +42796,16 @@
       <c r="H63" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I63" s="17">
+      <c r="I63" s="15">
         <v>1.3810035714285716</v>
       </c>
-      <c r="J63" s="17">
+      <c r="J63" s="15">
         <v>1.1398190476190477</v>
       </c>
-      <c r="K63" s="17">
+      <c r="K63" s="15">
         <v>0.95990595238095244</v>
       </c>
-      <c r="L63" s="17">
+      <c r="L63" s="15">
         <v>0.81155595238095224</v>
       </c>
     </row>
@@ -41248,16 +42828,16 @@
       <c r="H64" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I64" s="17">
+      <c r="I64" s="15">
         <v>1.3823535714285713</v>
       </c>
-      <c r="J64" s="17">
+      <c r="J64" s="15">
         <v>1.1411630952380953</v>
       </c>
-      <c r="K64" s="17">
+      <c r="K64" s="15">
         <v>0.95915238095238087</v>
       </c>
-      <c r="L64" s="17">
+      <c r="L64" s="15">
         <v>0.80872380952380951</v>
       </c>
     </row>
@@ -41280,16 +42860,16 @@
       <c r="H65" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I65" s="17">
+      <c r="I65" s="15">
         <v>1.3831476190476188</v>
       </c>
-      <c r="J65" s="17">
+      <c r="J65" s="15">
         <v>1.1423059523809522</v>
       </c>
-      <c r="K65" s="17">
+      <c r="K65" s="15">
         <v>0.95836428571428567</v>
       </c>
-      <c r="L65" s="17">
+      <c r="L65" s="15">
         <v>0.80563571428571457</v>
       </c>
     </row>
@@ -41312,16 +42892,16 @@
       <c r="H66" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I66" s="17">
+      <c r="I66" s="15">
         <v>1.3826880952380953</v>
       </c>
-      <c r="J66" s="17">
+      <c r="J66" s="15">
         <v>1.1428523809523807</v>
       </c>
-      <c r="K66" s="17">
+      <c r="K66" s="15">
         <v>0.95711666666666673</v>
       </c>
-      <c r="L66" s="17">
+      <c r="L66" s="15">
         <v>0.80209642857142871</v>
       </c>
     </row>
@@ -41344,16 +42924,16 @@
       <c r="H67" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I67" s="17">
+      <c r="I67" s="15">
         <v>1.3818869047619049</v>
       </c>
-      <c r="J67" s="17">
+      <c r="J67" s="15">
         <v>1.1433904761904763</v>
       </c>
-      <c r="K67" s="17">
+      <c r="K67" s="15">
         <v>0.95689880952380957</v>
       </c>
-      <c r="L67" s="17">
+      <c r="L67" s="15">
         <v>0.79989523809523833</v>
       </c>
     </row>
@@ -41376,16 +42956,16 @@
       <c r="H68" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I68" s="17">
+      <c r="I68" s="15">
         <v>1.3808773809523809</v>
       </c>
-      <c r="J68" s="17">
+      <c r="J68" s="15">
         <v>1.1440238095238093</v>
       </c>
-      <c r="K68" s="17">
+      <c r="K68" s="15">
         <v>0.95619166666666666</v>
       </c>
-      <c r="L68" s="17">
+      <c r="L68" s="15">
         <v>0.7966035714285713</v>
       </c>
     </row>
@@ -41408,16 +42988,16 @@
       <c r="H69" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I69" s="17">
+      <c r="I69" s="15">
         <v>1.3795154761904762</v>
       </c>
-      <c r="J69" s="17">
+      <c r="J69" s="15">
         <v>1.1447571428571428</v>
       </c>
-      <c r="K69" s="17">
+      <c r="K69" s="15">
         <v>0.95551547619047605</v>
       </c>
-      <c r="L69" s="17">
+      <c r="L69" s="15">
         <v>0.79342500000000005</v>
       </c>
     </row>
@@ -41440,16 +43020,16 @@
       <c r="H70" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I70" s="17">
+      <c r="I70" s="15">
         <v>1.3773190476190476</v>
       </c>
-      <c r="J70" s="17">
+      <c r="J70" s="15">
         <v>1.1488857142857143</v>
       </c>
-      <c r="K70" s="17">
+      <c r="K70" s="15">
         <v>0.95944166666666664</v>
       </c>
-      <c r="L70" s="17">
+      <c r="L70" s="15">
         <v>0.79526666666666657</v>
       </c>
     </row>
@@ -41472,16 +43052,16 @@
       <c r="H71" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I71" s="17">
+      <c r="I71" s="15">
         <v>1.3762702380952383</v>
       </c>
-      <c r="J71" s="17">
+      <c r="J71" s="15">
         <v>1.1461416666666666</v>
       </c>
-      <c r="K71" s="17">
+      <c r="K71" s="15">
         <v>0.95423095238095235</v>
       </c>
-      <c r="L71" s="17">
+      <c r="L71" s="15">
         <v>0.78675714285714282</v>
       </c>
     </row>
@@ -41504,16 +43084,16 @@
       <c r="H72" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I72" s="17">
+      <c r="I72" s="15">
         <v>1.3746654761904764</v>
       </c>
-      <c r="J72" s="17">
+      <c r="J72" s="15">
         <v>1.1470392857142857</v>
       </c>
-      <c r="K72" s="17">
+      <c r="K72" s="15">
         <v>0.95360238095238092</v>
       </c>
-      <c r="L72" s="17">
+      <c r="L72" s="15">
         <v>0.78339166666666671</v>
       </c>
     </row>
@@ -41536,16 +43116,16 @@
       <c r="H73" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I73" s="18">
+      <c r="I73">
         <v>1.3760292063492063</v>
       </c>
-      <c r="J73" s="18">
+      <c r="J73">
         <v>1.1409043650793651</v>
       </c>
-      <c r="K73" s="18">
+      <c r="K73">
         <v>0.95894547619047588</v>
       </c>
-      <c r="L73" s="18">
+      <c r="L73">
         <v>0.80537206349206358</v>
       </c>
     </row>
